--- a/calculadora_final_srt.xlsx
+++ b/calculadora_final_srt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aalvarez\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alfredo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9CC0FF6-E062-4524-AD5D-D3BD93431275}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="-90" windowWidth="20660" windowHeight="10260" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cervical" sheetId="1" r:id="rId1"/>
@@ -23,11 +23,6 @@
     <sheet name="Miembro Inferior Izquierdo" sheetId="9" r:id="rId8"/>
   </sheets>
   <calcPr calcId="124519"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -1884,14 +1879,10 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1929,9 +1920,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1964,26 +1955,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2016,26 +1990,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2210,16 +2167,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G46"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="21.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="21.86328125" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="3" width="21.85546875" style="5"/>
-    <col min="4" max="5" width="62.85546875" style="5" customWidth="1"/>
+    <col min="1" max="3" width="21.86328125" style="5"/>
+    <col min="4" max="5" width="62.86328125" style="5" customWidth="1"/>
     <col min="6" max="6" width="53" style="5" customWidth="1"/>
-    <col min="7" max="7" width="21.85546875" style="4"/>
-    <col min="8" max="16384" width="21.85546875" style="5"/>
+    <col min="7" max="7" width="21.86328125" style="4"/>
+    <col min="8" max="16384" width="21.86328125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" s="6" customFormat="1" x14ac:dyDescent="0.75">
       <c r="A1" s="6" t="s">
         <v>541</v>
       </c>
@@ -2242,7 +2199,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A2" s="5" t="s">
         <v>5</v>
       </c>
@@ -2265,7 +2222,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A3" s="5" t="s">
         <v>5</v>
       </c>
@@ -2288,7 +2245,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A4" s="5" t="s">
         <v>5</v>
       </c>
@@ -2311,7 +2268,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A5" s="5" t="s">
         <v>5</v>
       </c>
@@ -2334,7 +2291,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A6" s="5" t="s">
         <v>5</v>
       </c>
@@ -2357,7 +2314,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A7" s="5" t="s">
         <v>5</v>
       </c>
@@ -2380,7 +2337,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A8" s="5" t="s">
         <v>5</v>
       </c>
@@ -2403,7 +2360,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A9" s="5" t="s">
         <v>5</v>
       </c>
@@ -2426,7 +2383,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A10" s="5" t="s">
         <v>5</v>
       </c>
@@ -2449,7 +2406,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A11" s="5" t="s">
         <v>5</v>
       </c>
@@ -2472,7 +2429,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A12" s="5" t="s">
         <v>5</v>
       </c>
@@ -2495,7 +2452,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A13" s="5" t="s">
         <v>5</v>
       </c>
@@ -2518,7 +2475,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A14" s="5" t="s">
         <v>5</v>
       </c>
@@ -2541,7 +2498,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A15" s="5" t="s">
         <v>5</v>
       </c>
@@ -2564,7 +2521,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A16" s="5" t="s">
         <v>5</v>
       </c>
@@ -2587,7 +2544,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A17" s="5" t="s">
         <v>5</v>
       </c>
@@ -2610,7 +2567,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A18" s="5" t="s">
         <v>5</v>
       </c>
@@ -2633,7 +2590,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A19" s="5" t="s">
         <v>5</v>
       </c>
@@ -2656,7 +2613,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A20" s="5" t="s">
         <v>5</v>
       </c>
@@ -2679,7 +2636,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A21" s="5" t="s">
         <v>5</v>
       </c>
@@ -2702,7 +2659,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A22" s="5" t="s">
         <v>5</v>
       </c>
@@ -2725,7 +2682,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A23" s="5" t="s">
         <v>5</v>
       </c>
@@ -2748,7 +2705,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A24" s="5" t="s">
         <v>5</v>
       </c>
@@ -2771,7 +2728,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A25" s="5" t="s">
         <v>5</v>
       </c>
@@ -2794,7 +2751,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A26" s="5" t="s">
         <v>5</v>
       </c>
@@ -2817,7 +2774,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A27" s="5" t="s">
         <v>5</v>
       </c>
@@ -2840,7 +2797,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A28" s="5" t="s">
         <v>5</v>
       </c>
@@ -2863,7 +2820,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A29" s="5" t="s">
         <v>5</v>
       </c>
@@ -2886,7 +2843,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A30" s="5" t="s">
         <v>5</v>
       </c>
@@ -2909,7 +2866,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A31" s="5" t="s">
         <v>5</v>
       </c>
@@ -2932,7 +2889,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A32" s="5" t="s">
         <v>5</v>
       </c>
@@ -2955,7 +2912,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A33" s="5" t="s">
         <v>5</v>
       </c>
@@ -2978,7 +2935,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A34" s="5" t="s">
         <v>5</v>
       </c>
@@ -3001,7 +2958,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A35" s="5" t="s">
         <v>5</v>
       </c>
@@ -3024,7 +2981,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A36" s="5" t="s">
         <v>5</v>
       </c>
@@ -3047,7 +3004,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A37" s="5" t="s">
         <v>5</v>
       </c>
@@ -3070,7 +3027,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A38" s="5" t="s">
         <v>5</v>
       </c>
@@ -3093,7 +3050,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A39" s="5" t="s">
         <v>5</v>
       </c>
@@ -3116,7 +3073,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A40" s="5" t="s">
         <v>5</v>
       </c>
@@ -3139,7 +3096,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A41" s="5" t="s">
         <v>5</v>
       </c>
@@ -3162,7 +3119,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A42" s="5" t="s">
         <v>5</v>
       </c>
@@ -3185,7 +3142,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A43" s="5" t="s">
         <v>5</v>
       </c>
@@ -3208,7 +3165,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A44" s="5" t="s">
         <v>5</v>
       </c>
@@ -3231,7 +3188,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A45" s="5" t="s">
         <v>5</v>
       </c>
@@ -3254,7 +3211,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A46" s="5" t="s">
         <v>5</v>
       </c>
@@ -3286,18 +3243,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="77.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="77.26953125" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="31.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="23.28515625" style="1" customWidth="1"/>
-    <col min="4" max="5" width="61.28515625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="53.7109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="25.85546875" style="8" customWidth="1"/>
-    <col min="8" max="16384" width="77.28515625" style="1"/>
+    <col min="1" max="1" width="31.7265625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="30.40625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="23.26953125" style="1" customWidth="1"/>
+    <col min="4" max="5" width="61.26953125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="53.7265625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="25.86328125" style="8" customWidth="1"/>
+    <col min="8" max="16384" width="77.26953125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.75">
       <c r="A1" s="2" t="s">
         <v>541</v>
       </c>
@@ -3320,7 +3277,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -3340,7 +3297,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -3360,7 +3317,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -3380,7 +3337,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -3400,7 +3357,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -3420,7 +3377,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -3440,7 +3397,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A8" s="1" t="s">
         <v>5</v>
       </c>
@@ -3463,7 +3420,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A9" s="1" t="s">
         <v>5</v>
       </c>
@@ -3486,7 +3443,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A10" s="1" t="s">
         <v>5</v>
       </c>
@@ -3509,7 +3466,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A11" s="1" t="s">
         <v>5</v>
       </c>
@@ -3532,7 +3489,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A12" s="1" t="s">
         <v>5</v>
       </c>
@@ -3555,7 +3512,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A13" s="1" t="s">
         <v>5</v>
       </c>
@@ -3587,17 +3544,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G37"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="36" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="36" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="1" max="3" width="36" style="1"/>
-    <col min="4" max="4" width="61.28515625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="61.26953125" style="1" customWidth="1"/>
     <col min="5" max="5" width="36" style="1"/>
-    <col min="6" max="6" width="45.5703125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="45.54296875" style="1" customWidth="1"/>
     <col min="7" max="7" width="36" style="8"/>
     <col min="8" max="16384" width="36" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.75">
       <c r="A1" s="2" t="s">
         <v>541</v>
       </c>
@@ -3620,7 +3577,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -3640,7 +3597,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -3660,7 +3617,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -3680,7 +3637,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -3700,7 +3657,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -3720,7 +3677,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -3740,7 +3697,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A8" s="1" t="s">
         <v>5</v>
       </c>
@@ -3763,7 +3720,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A9" s="1" t="s">
         <v>5</v>
       </c>
@@ -3786,7 +3743,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A10" s="1" t="s">
         <v>5</v>
       </c>
@@ -3809,7 +3766,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A11" s="1" t="s">
         <v>5</v>
       </c>
@@ -3832,7 +3789,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A12" s="1" t="s">
         <v>5</v>
       </c>
@@ -3855,7 +3812,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A13" s="1" t="s">
         <v>5</v>
       </c>
@@ -3878,7 +3835,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A14" s="1" t="s">
         <v>5</v>
       </c>
@@ -3901,7 +3858,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A15" s="1" t="s">
         <v>5</v>
       </c>
@@ -3924,7 +3881,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A16" s="1" t="s">
         <v>5</v>
       </c>
@@ -3947,7 +3904,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A17" s="1" t="s">
         <v>5</v>
       </c>
@@ -3970,7 +3927,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A18" s="1" t="s">
         <v>5</v>
       </c>
@@ -3993,7 +3950,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A19" s="1" t="s">
         <v>5</v>
       </c>
@@ -4016,7 +3973,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A20" s="1" t="s">
         <v>5</v>
       </c>
@@ -4039,7 +3996,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A21" s="1" t="s">
         <v>5</v>
       </c>
@@ -4062,7 +4019,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A22" s="1" t="s">
         <v>5</v>
       </c>
@@ -4085,7 +4042,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A23" s="1" t="s">
         <v>5</v>
       </c>
@@ -4108,7 +4065,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A24" s="1" t="s">
         <v>5</v>
       </c>
@@ -4131,7 +4088,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A25" s="1" t="s">
         <v>5</v>
       </c>
@@ -4154,7 +4111,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A26" s="1" t="s">
         <v>5</v>
       </c>
@@ -4177,7 +4134,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A27" s="1" t="s">
         <v>5</v>
       </c>
@@ -4200,7 +4157,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A28" s="1" t="s">
         <v>5</v>
       </c>
@@ -4223,7 +4180,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A29" s="1" t="s">
         <v>5</v>
       </c>
@@ -4246,7 +4203,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A30" s="1" t="s">
         <v>5</v>
       </c>
@@ -4269,7 +4226,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A31" s="1" t="s">
         <v>5</v>
       </c>
@@ -4292,7 +4249,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A32" s="1" t="s">
         <v>5</v>
       </c>
@@ -4315,7 +4272,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A33" s="1" t="s">
         <v>5</v>
       </c>
@@ -4338,7 +4295,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A34" s="1" t="s">
         <v>5</v>
       </c>
@@ -4361,7 +4318,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A35" s="1" t="s">
         <v>5</v>
       </c>
@@ -4384,7 +4341,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A36" s="1" t="s">
         <v>5</v>
       </c>
@@ -4407,7 +4364,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A37" s="1" t="s">
         <v>5</v>
       </c>
@@ -4438,17 +4395,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="27.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="27.54296875" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="3" width="27.5703125" style="1"/>
-    <col min="4" max="4" width="65.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="30.7109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="68.28515625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="27.5703125" style="8"/>
-    <col min="8" max="16384" width="27.5703125" style="1"/>
+    <col min="1" max="3" width="27.54296875" style="1"/>
+    <col min="4" max="4" width="65.40625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="30.7265625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="68.26953125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="27.54296875" style="8"/>
+    <col min="8" max="16384" width="27.54296875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.75">
       <c r="A1" s="2" t="s">
         <v>541</v>
       </c>
@@ -4471,7 +4428,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -4491,7 +4448,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -4511,7 +4468,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -4531,7 +4488,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -4554,7 +4511,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -4577,7 +4534,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -4600,7 +4557,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A8" s="1" t="s">
         <v>5</v>
       </c>
@@ -4623,7 +4580,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A9" s="1" t="s">
         <v>5</v>
       </c>
@@ -4646,7 +4603,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A10" s="1" t="s">
         <v>5</v>
       </c>
@@ -4669,7 +4626,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A11" s="1" t="s">
         <v>5</v>
       </c>
@@ -4689,7 +4646,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A12" s="1" t="s">
         <v>5</v>
       </c>
@@ -4709,7 +4666,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A13" s="1" t="s">
         <v>5</v>
       </c>
@@ -4738,16 +4695,16 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:G269"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="27.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="27.1328125" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="3" width="27.140625" style="1"/>
+    <col min="1" max="3" width="27.1328125" style="1"/>
     <col min="4" max="4" width="43" style="1" customWidth="1"/>
-    <col min="5" max="5" width="45.28515625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="97.5703125" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="27.140625" style="1"/>
+    <col min="5" max="5" width="45.26953125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="97.54296875" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="27.1328125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.75">
       <c r="A1" s="2" t="s">
         <v>541</v>
       </c>
@@ -4770,7 +4727,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -4793,7 +4750,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -4816,7 +4773,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -4839,7 +4796,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -4862,7 +4819,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -4885,7 +4842,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -4908,7 +4865,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A8" s="1" t="s">
         <v>5</v>
       </c>
@@ -4931,7 +4888,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A9" s="1" t="s">
         <v>5</v>
       </c>
@@ -4954,7 +4911,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A10" s="1" t="s">
         <v>5</v>
       </c>
@@ -4977,7 +4934,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A11" s="1" t="s">
         <v>5</v>
       </c>
@@ -5000,7 +4957,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A12" s="1" t="s">
         <v>5</v>
       </c>
@@ -5023,7 +4980,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A13" s="1" t="s">
         <v>5</v>
       </c>
@@ -5046,7 +5003,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A14" s="1" t="s">
         <v>5</v>
       </c>
@@ -5069,7 +5026,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A15" s="1" t="s">
         <v>5</v>
       </c>
@@ -5092,7 +5049,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A16" s="1" t="s">
         <v>5</v>
       </c>
@@ -5115,7 +5072,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A17" s="1" t="s">
         <v>5</v>
       </c>
@@ -5138,7 +5095,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A18" s="1" t="s">
         <v>5</v>
       </c>
@@ -5161,7 +5118,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A19" s="1" t="s">
         <v>5</v>
       </c>
@@ -5184,7 +5141,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A20" s="1" t="s">
         <v>5</v>
       </c>
@@ -5207,7 +5164,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A21" s="1" t="s">
         <v>5</v>
       </c>
@@ -5230,7 +5187,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A22" s="1" t="s">
         <v>5</v>
       </c>
@@ -5253,7 +5210,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A23" s="1" t="s">
         <v>5</v>
       </c>
@@ -5276,7 +5233,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A24" s="1" t="s">
         <v>5</v>
       </c>
@@ -5299,7 +5256,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A25" s="1" t="s">
         <v>5</v>
       </c>
@@ -5322,7 +5279,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A26" s="1" t="s">
         <v>5</v>
       </c>
@@ -5345,7 +5302,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A27" s="1" t="s">
         <v>5</v>
       </c>
@@ -5368,7 +5325,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A28" s="1" t="s">
         <v>5</v>
       </c>
@@ -5391,7 +5348,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A29" s="1" t="s">
         <v>5</v>
       </c>
@@ -5414,7 +5371,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A30" s="1" t="s">
         <v>5</v>
       </c>
@@ -5437,7 +5394,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A31" s="1" t="s">
         <v>5</v>
       </c>
@@ -5460,7 +5417,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A32" s="1" t="s">
         <v>5</v>
       </c>
@@ -5483,7 +5440,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A33" s="1" t="s">
         <v>5</v>
       </c>
@@ -5506,7 +5463,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A34" s="1" t="s">
         <v>5</v>
       </c>
@@ -5529,7 +5486,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A35" s="1" t="s">
         <v>5</v>
       </c>
@@ -5552,7 +5509,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A36" s="1" t="s">
         <v>5</v>
       </c>
@@ -5575,7 +5532,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A37" s="1" t="s">
         <v>5</v>
       </c>
@@ -5598,7 +5555,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A38" s="1" t="s">
         <v>5</v>
       </c>
@@ -5621,7 +5578,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A39" s="1" t="s">
         <v>5</v>
       </c>
@@ -5644,7 +5601,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A40" s="1" t="s">
         <v>5</v>
       </c>
@@ -5667,7 +5624,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A41" s="1" t="s">
         <v>5</v>
       </c>
@@ -5690,7 +5647,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A42" s="1" t="s">
         <v>5</v>
       </c>
@@ -5713,7 +5670,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A43" s="1" t="s">
         <v>5</v>
       </c>
@@ -5736,7 +5693,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A44" s="1" t="s">
         <v>5</v>
       </c>
@@ -5759,7 +5716,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A45" s="1" t="s">
         <v>5</v>
       </c>
@@ -5782,7 +5739,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A46" s="1" t="s">
         <v>5</v>
       </c>
@@ -5805,7 +5762,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A47" s="1" t="s">
         <v>5</v>
       </c>
@@ -5828,7 +5785,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A48" s="1" t="s">
         <v>5</v>
       </c>
@@ -5851,7 +5808,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A49" s="1" t="s">
         <v>5</v>
       </c>
@@ -5874,7 +5831,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A50" s="1" t="s">
         <v>5</v>
       </c>
@@ -5897,7 +5854,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A51" s="1" t="s">
         <v>5</v>
       </c>
@@ -5920,7 +5877,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A52" s="1" t="s">
         <v>5</v>
       </c>
@@ -5943,7 +5900,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A53" s="1" t="s">
         <v>5</v>
       </c>
@@ -5966,7 +5923,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A54" s="1" t="s">
         <v>5</v>
       </c>
@@ -5989,7 +5946,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A55" s="1" t="s">
         <v>5</v>
       </c>
@@ -6012,7 +5969,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A56" s="1" t="s">
         <v>5</v>
       </c>
@@ -6035,7 +5992,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A57" s="1" t="s">
         <v>5</v>
       </c>
@@ -6058,7 +6015,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A58" s="1" t="s">
         <v>5</v>
       </c>
@@ -6081,7 +6038,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A59" s="1" t="s">
         <v>5</v>
       </c>
@@ -6104,7 +6061,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A60" s="1" t="s">
         <v>5</v>
       </c>
@@ -6127,7 +6084,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A61" s="1" t="s">
         <v>5</v>
       </c>
@@ -6150,7 +6107,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A62" s="1" t="s">
         <v>5</v>
       </c>
@@ -6173,7 +6130,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A63" s="1" t="s">
         <v>5</v>
       </c>
@@ -6196,7 +6153,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A64" s="1" t="s">
         <v>5</v>
       </c>
@@ -6219,7 +6176,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A65" s="1" t="s">
         <v>5</v>
       </c>
@@ -6242,7 +6199,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A66" s="1" t="s">
         <v>5</v>
       </c>
@@ -6265,7 +6222,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A67" s="1" t="s">
         <v>5</v>
       </c>
@@ -6288,7 +6245,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A68" s="1" t="s">
         <v>5</v>
       </c>
@@ -6311,7 +6268,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A69" s="1" t="s">
         <v>5</v>
       </c>
@@ -6334,7 +6291,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A70" s="1" t="s">
         <v>5</v>
       </c>
@@ -6357,7 +6314,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A71" s="1" t="s">
         <v>5</v>
       </c>
@@ -6380,7 +6337,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A72" s="1" t="s">
         <v>5</v>
       </c>
@@ -6403,7 +6360,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A73" s="1" t="s">
         <v>5</v>
       </c>
@@ -6426,7 +6383,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A74" s="1" t="s">
         <v>5</v>
       </c>
@@ -6449,7 +6406,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A75" s="1" t="s">
         <v>5</v>
       </c>
@@ -6472,7 +6429,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A76" s="1" t="s">
         <v>5</v>
       </c>
@@ -6495,7 +6452,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A77" s="1" t="s">
         <v>5</v>
       </c>
@@ -6518,7 +6475,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A78" s="1" t="s">
         <v>5</v>
       </c>
@@ -6541,7 +6498,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A79" s="1" t="s">
         <v>5</v>
       </c>
@@ -6564,7 +6521,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A80" s="1" t="s">
         <v>5</v>
       </c>
@@ -6587,7 +6544,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A81" s="1" t="s">
         <v>5</v>
       </c>
@@ -6610,7 +6567,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A82" s="1" t="s">
         <v>5</v>
       </c>
@@ -6633,7 +6590,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A83" s="1" t="s">
         <v>5</v>
       </c>
@@ -6653,7 +6610,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A84" s="1" t="s">
         <v>5</v>
       </c>
@@ -6673,7 +6630,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A85" s="1" t="s">
         <v>5</v>
       </c>
@@ -6693,7 +6650,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A86" s="1" t="s">
         <v>5</v>
       </c>
@@ -6713,7 +6670,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A87" s="1" t="s">
         <v>5</v>
       </c>
@@ -6733,7 +6690,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A88" s="1" t="s">
         <v>5</v>
       </c>
@@ -6753,7 +6710,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A89" s="1" t="s">
         <v>5</v>
       </c>
@@ -6773,7 +6730,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A90" s="1" t="s">
         <v>5</v>
       </c>
@@ -6793,7 +6750,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A91" s="1" t="s">
         <v>5</v>
       </c>
@@ -6813,7 +6770,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A92" s="1" t="s">
         <v>5</v>
       </c>
@@ -6833,7 +6790,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A93" s="1" t="s">
         <v>5</v>
       </c>
@@ -6853,7 +6810,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A94" s="1" t="s">
         <v>5</v>
       </c>
@@ -6873,7 +6830,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A95" s="1" t="s">
         <v>5</v>
       </c>
@@ -6893,7 +6850,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A96" s="1" t="s">
         <v>5</v>
       </c>
@@ -6913,7 +6870,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A97" s="1" t="s">
         <v>5</v>
       </c>
@@ -6933,7 +6890,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A98" s="1" t="s">
         <v>5</v>
       </c>
@@ -6953,7 +6910,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A99" s="1" t="s">
         <v>5</v>
       </c>
@@ -6973,7 +6930,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A100" s="1" t="s">
         <v>5</v>
       </c>
@@ -6993,7 +6950,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A101" s="1" t="s">
         <v>5</v>
       </c>
@@ -7013,7 +6970,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A102" s="1" t="s">
         <v>5</v>
       </c>
@@ -7033,7 +6990,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A103" s="1" t="s">
         <v>5</v>
       </c>
@@ -7053,7 +7010,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A104" s="1" t="s">
         <v>5</v>
       </c>
@@ -7073,7 +7030,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A105" s="1" t="s">
         <v>5</v>
       </c>
@@ -7093,7 +7050,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A106" s="1" t="s">
         <v>5</v>
       </c>
@@ -7113,7 +7070,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A107" s="1" t="s">
         <v>5</v>
       </c>
@@ -7133,7 +7090,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A108" s="1" t="s">
         <v>5</v>
       </c>
@@ -7153,7 +7110,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A109" s="1" t="s">
         <v>5</v>
       </c>
@@ -7173,7 +7130,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A110" s="1" t="s">
         <v>5</v>
       </c>
@@ -7193,7 +7150,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A111" s="1" t="s">
         <v>5</v>
       </c>
@@ -7213,7 +7170,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A112" s="1" t="s">
         <v>5</v>
       </c>
@@ -7233,7 +7190,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A113" s="1" t="s">
         <v>5</v>
       </c>
@@ -7253,7 +7210,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A114" s="1" t="s">
         <v>5</v>
       </c>
@@ -7273,7 +7230,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A115" s="1" t="s">
         <v>5</v>
       </c>
@@ -7293,7 +7250,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A116" s="1" t="s">
         <v>5</v>
       </c>
@@ -7313,7 +7270,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A117" s="1" t="s">
         <v>5</v>
       </c>
@@ -7333,7 +7290,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A118" s="1" t="s">
         <v>5</v>
       </c>
@@ -7353,7 +7310,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A119" s="1" t="s">
         <v>5</v>
       </c>
@@ -7373,7 +7330,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A120" s="1" t="s">
         <v>5</v>
       </c>
@@ -7393,7 +7350,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A121" s="1" t="s">
         <v>5</v>
       </c>
@@ -7413,7 +7370,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A122" s="1" t="s">
         <v>5</v>
       </c>
@@ -7433,7 +7390,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A123" s="1" t="s">
         <v>5</v>
       </c>
@@ -7453,7 +7410,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A124" s="1" t="s">
         <v>5</v>
       </c>
@@ -7473,7 +7430,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A125" s="1" t="s">
         <v>5</v>
       </c>
@@ -7493,7 +7450,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A126" s="1" t="s">
         <v>5</v>
       </c>
@@ -7513,7 +7470,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A127" s="1" t="s">
         <v>5</v>
       </c>
@@ -7533,7 +7490,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A128" s="1" t="s">
         <v>5</v>
       </c>
@@ -7553,7 +7510,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A129" s="1" t="s">
         <v>5</v>
       </c>
@@ -7573,7 +7530,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A130" s="1" t="s">
         <v>5</v>
       </c>
@@ -7593,7 +7550,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A131" s="1" t="s">
         <v>5</v>
       </c>
@@ -7613,7 +7570,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A132" s="1" t="s">
         <v>5</v>
       </c>
@@ -7633,7 +7590,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A133" s="1" t="s">
         <v>5</v>
       </c>
@@ -7653,7 +7610,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A134" s="1" t="s">
         <v>5</v>
       </c>
@@ -7673,7 +7630,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A135" s="1" t="s">
         <v>5</v>
       </c>
@@ -7693,7 +7650,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A136" s="1" t="s">
         <v>5</v>
       </c>
@@ -7713,7 +7670,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A137" s="1" t="s">
         <v>5</v>
       </c>
@@ -7733,7 +7690,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A138" s="1" t="s">
         <v>5</v>
       </c>
@@ -7753,7 +7710,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A139" s="1" t="s">
         <v>5</v>
       </c>
@@ -7773,7 +7730,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A140" s="1" t="s">
         <v>5</v>
       </c>
@@ -7793,7 +7750,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A141" s="1" t="s">
         <v>5</v>
       </c>
@@ -7813,7 +7770,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A142" s="1" t="s">
         <v>5</v>
       </c>
@@ -7833,7 +7790,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A143" s="1" t="s">
         <v>5</v>
       </c>
@@ -7853,7 +7810,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A144" s="1" t="s">
         <v>5</v>
       </c>
@@ -7873,7 +7830,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A145" s="1" t="s">
         <v>5</v>
       </c>
@@ -7893,7 +7850,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A146" s="1" t="s">
         <v>5</v>
       </c>
@@ -7913,7 +7870,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A147" s="1" t="s">
         <v>5</v>
       </c>
@@ -7933,7 +7890,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A148" s="1" t="s">
         <v>5</v>
       </c>
@@ -7953,7 +7910,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A149" s="1" t="s">
         <v>5</v>
       </c>
@@ -7973,7 +7930,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A150" s="1" t="s">
         <v>5</v>
       </c>
@@ -7993,7 +7950,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A151" s="1" t="s">
         <v>5</v>
       </c>
@@ -8013,7 +7970,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A152" s="1" t="s">
         <v>5</v>
       </c>
@@ -8033,7 +7990,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A153" s="1" t="s">
         <v>5</v>
       </c>
@@ -8053,7 +8010,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A154" s="1" t="s">
         <v>5</v>
       </c>
@@ -8073,7 +8030,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A155" s="1" t="s">
         <v>5</v>
       </c>
@@ -8093,7 +8050,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A156" s="1" t="s">
         <v>5</v>
       </c>
@@ -8113,7 +8070,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A157" s="1" t="s">
         <v>5</v>
       </c>
@@ -8133,7 +8090,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A158" s="1" t="s">
         <v>5</v>
       </c>
@@ -8153,7 +8110,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A159" s="1" t="s">
         <v>5</v>
       </c>
@@ -8173,7 +8130,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A160" s="1" t="s">
         <v>5</v>
       </c>
@@ -8193,7 +8150,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A161" s="1" t="s">
         <v>5</v>
       </c>
@@ -8213,7 +8170,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A162" s="1" t="s">
         <v>5</v>
       </c>
@@ -8233,7 +8190,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A163" s="1" t="s">
         <v>5</v>
       </c>
@@ -8253,7 +8210,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A164" s="1" t="s">
         <v>5</v>
       </c>
@@ -8273,7 +8230,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A165" s="1" t="s">
         <v>5</v>
       </c>
@@ -8293,7 +8250,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A166" s="1" t="s">
         <v>5</v>
       </c>
@@ -8313,7 +8270,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A167" s="1" t="s">
         <v>5</v>
       </c>
@@ -8333,7 +8290,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A168" s="1" t="s">
         <v>5</v>
       </c>
@@ -8353,7 +8310,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A169" s="1" t="s">
         <v>5</v>
       </c>
@@ -8373,7 +8330,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A170" s="1" t="s">
         <v>5</v>
       </c>
@@ -8393,7 +8350,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A171" s="1" t="s">
         <v>5</v>
       </c>
@@ -8413,7 +8370,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A172" s="1" t="s">
         <v>5</v>
       </c>
@@ -8433,7 +8390,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A173" s="1" t="s">
         <v>5</v>
       </c>
@@ -8453,7 +8410,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A174" s="1" t="s">
         <v>5</v>
       </c>
@@ -8473,7 +8430,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A175" s="1" t="s">
         <v>5</v>
       </c>
@@ -8493,7 +8450,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A176" s="1" t="s">
         <v>5</v>
       </c>
@@ -8513,7 +8470,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A177" s="1" t="s">
         <v>5</v>
       </c>
@@ -8533,7 +8490,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A178" s="1" t="s">
         <v>5</v>
       </c>
@@ -8553,7 +8510,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A179" s="1" t="s">
         <v>5</v>
       </c>
@@ -8573,7 +8530,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A180" s="1" t="s">
         <v>5</v>
       </c>
@@ -8593,7 +8550,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A181" s="1" t="s">
         <v>5</v>
       </c>
@@ -8613,7 +8570,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A182" s="1" t="s">
         <v>5</v>
       </c>
@@ -8633,7 +8590,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A183" s="1" t="s">
         <v>5</v>
       </c>
@@ -8653,7 +8610,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A184" s="1" t="s">
         <v>5</v>
       </c>
@@ -8673,7 +8630,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A185" s="1" t="s">
         <v>5</v>
       </c>
@@ -8693,7 +8650,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A186" s="1" t="s">
         <v>5</v>
       </c>
@@ -8713,7 +8670,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A187" s="1" t="s">
         <v>5</v>
       </c>
@@ -8733,7 +8690,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A188" s="1" t="s">
         <v>5</v>
       </c>
@@ -8753,7 +8710,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A189" s="1" t="s">
         <v>5</v>
       </c>
@@ -8773,7 +8730,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A190" s="1" t="s">
         <v>5</v>
       </c>
@@ -8793,7 +8750,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A191" s="1" t="s">
         <v>5</v>
       </c>
@@ -8813,7 +8770,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A192" s="1" t="s">
         <v>5</v>
       </c>
@@ -8833,7 +8790,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A193" s="1" t="s">
         <v>5</v>
       </c>
@@ -8853,7 +8810,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A194" s="1" t="s">
         <v>5</v>
       </c>
@@ -8873,7 +8830,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A195" s="1" t="s">
         <v>5</v>
       </c>
@@ -8893,7 +8850,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A196" s="1" t="s">
         <v>5</v>
       </c>
@@ -8913,7 +8870,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A197" s="1" t="s">
         <v>5</v>
       </c>
@@ -8933,7 +8890,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A198" s="1" t="s">
         <v>5</v>
       </c>
@@ -8953,7 +8910,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A199" s="1" t="s">
         <v>5</v>
       </c>
@@ -8973,7 +8930,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A200" s="1" t="s">
         <v>5</v>
       </c>
@@ -8993,7 +8950,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A201" s="1" t="s">
         <v>5</v>
       </c>
@@ -9013,7 +8970,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A202" s="1" t="s">
         <v>5</v>
       </c>
@@ -9033,7 +8990,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A203" s="1" t="s">
         <v>5</v>
       </c>
@@ -9053,7 +9010,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A204" s="1" t="s">
         <v>5</v>
       </c>
@@ -9073,7 +9030,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A205" s="1" t="s">
         <v>5</v>
       </c>
@@ -9093,7 +9050,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A206" s="1" t="s">
         <v>5</v>
       </c>
@@ -9113,7 +9070,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A207" s="1" t="s">
         <v>5</v>
       </c>
@@ -9133,7 +9090,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A208" s="1" t="s">
         <v>5</v>
       </c>
@@ -9153,7 +9110,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A209" s="1" t="s">
         <v>5</v>
       </c>
@@ -9173,7 +9130,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A210" s="1" t="s">
         <v>5</v>
       </c>
@@ -9193,7 +9150,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A211" s="1" t="s">
         <v>5</v>
       </c>
@@ -9213,7 +9170,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A212" s="1" t="s">
         <v>5</v>
       </c>
@@ -9233,7 +9190,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A213" s="1" t="s">
         <v>5</v>
       </c>
@@ -9253,7 +9210,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A214" s="1" t="s">
         <v>5</v>
       </c>
@@ -9273,7 +9230,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A215" s="1" t="s">
         <v>5</v>
       </c>
@@ -9293,7 +9250,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A216" s="1" t="s">
         <v>5</v>
       </c>
@@ -9313,7 +9270,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A217" s="1" t="s">
         <v>5</v>
       </c>
@@ -9333,7 +9290,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A218" s="1" t="s">
         <v>5</v>
       </c>
@@ -9353,7 +9310,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A219" s="1" t="s">
         <v>5</v>
       </c>
@@ -9373,7 +9330,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A220" s="1" t="s">
         <v>5</v>
       </c>
@@ -9393,7 +9350,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A221" s="1" t="s">
         <v>5</v>
       </c>
@@ -9413,7 +9370,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A222" s="1" t="s">
         <v>5</v>
       </c>
@@ -9433,7 +9390,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A223" s="1" t="s">
         <v>5</v>
       </c>
@@ -9453,7 +9410,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A224" s="1" t="s">
         <v>5</v>
       </c>
@@ -9473,7 +9430,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A225" s="1" t="s">
         <v>5</v>
       </c>
@@ -9493,7 +9450,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A226" s="1" t="s">
         <v>5</v>
       </c>
@@ -9513,7 +9470,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A227" s="1" t="s">
         <v>5</v>
       </c>
@@ -9533,7 +9490,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A228" s="1" t="s">
         <v>5</v>
       </c>
@@ -9553,7 +9510,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A229" s="1" t="s">
         <v>5</v>
       </c>
@@ -9573,7 +9530,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A230" s="1" t="s">
         <v>5</v>
       </c>
@@ -9593,7 +9550,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A231" s="1" t="s">
         <v>5</v>
       </c>
@@ -9613,7 +9570,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A232" s="1" t="s">
         <v>5</v>
       </c>
@@ -9633,7 +9590,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A233" s="1" t="s">
         <v>5</v>
       </c>
@@ -9653,7 +9610,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A234" s="1" t="s">
         <v>5</v>
       </c>
@@ -9673,7 +9630,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A235" s="1" t="s">
         <v>5</v>
       </c>
@@ -9693,7 +9650,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A236" s="1" t="s">
         <v>5</v>
       </c>
@@ -9713,7 +9670,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A237" s="1" t="s">
         <v>5</v>
       </c>
@@ -9733,7 +9690,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A238" s="1" t="s">
         <v>5</v>
       </c>
@@ -9753,7 +9710,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A239" s="1" t="s">
         <v>5</v>
       </c>
@@ -9773,7 +9730,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A240" s="1" t="s">
         <v>5</v>
       </c>
@@ -9793,7 +9750,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A241" s="1" t="s">
         <v>5</v>
       </c>
@@ -9813,7 +9770,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A242" s="1" t="s">
         <v>5</v>
       </c>
@@ -9833,7 +9790,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A243" s="1" t="s">
         <v>5</v>
       </c>
@@ -9853,7 +9810,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A244" s="1" t="s">
         <v>5</v>
       </c>
@@ -9873,7 +9830,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A245" s="1" t="s">
         <v>5</v>
       </c>
@@ -9893,7 +9850,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A246" s="1" t="s">
         <v>5</v>
       </c>
@@ -9913,7 +9870,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A247" s="1" t="s">
         <v>5</v>
       </c>
@@ -9933,7 +9890,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A248" s="1" t="s">
         <v>5</v>
       </c>
@@ -9953,7 +9910,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A249" s="1" t="s">
         <v>5</v>
       </c>
@@ -9973,7 +9930,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A250" s="1" t="s">
         <v>5</v>
       </c>
@@ -9993,7 +9950,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A251" s="1" t="s">
         <v>5</v>
       </c>
@@ -10013,7 +9970,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A252" s="1" t="s">
         <v>5</v>
       </c>
@@ -10033,7 +9990,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A253" s="1" t="s">
         <v>5</v>
       </c>
@@ -10053,7 +10010,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A254" s="1" t="s">
         <v>5</v>
       </c>
@@ -10073,7 +10030,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A255" s="1" t="s">
         <v>5</v>
       </c>
@@ -10093,7 +10050,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A256" s="1" t="s">
         <v>5</v>
       </c>
@@ -10113,7 +10070,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A257" s="1" t="s">
         <v>5</v>
       </c>
@@ -10133,7 +10090,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A258" s="1" t="s">
         <v>5</v>
       </c>
@@ -10153,7 +10110,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A259" s="1" t="s">
         <v>5</v>
       </c>
@@ -10173,7 +10130,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A260" s="1" t="s">
         <v>5</v>
       </c>
@@ -10193,7 +10150,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A261" s="1" t="s">
         <v>5</v>
       </c>
@@ -10213,7 +10170,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A262" s="1" t="s">
         <v>5</v>
       </c>
@@ -10233,7 +10190,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A263" s="1" t="s">
         <v>5</v>
       </c>
@@ -10253,7 +10210,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A264" s="1" t="s">
         <v>5</v>
       </c>
@@ -10273,7 +10230,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A265" s="1" t="s">
         <v>5</v>
       </c>
@@ -10293,7 +10250,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A266" s="1" t="s">
         <v>5</v>
       </c>
@@ -10313,7 +10270,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A267" s="1" t="s">
         <v>5</v>
       </c>
@@ -10333,7 +10290,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A268" s="1" t="s">
         <v>5</v>
       </c>
@@ -10353,7 +10310,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A269" s="1" t="s">
         <v>5</v>
       </c>
@@ -10381,15 +10338,15 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:F269"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="27.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="27.1328125" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="3" width="27.140625" style="1"/>
+    <col min="1" max="3" width="27.1328125" style="1"/>
     <col min="4" max="4" width="43" style="1" customWidth="1"/>
-    <col min="5" max="5" width="97.5703125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="27.140625" style="1"/>
+    <col min="5" max="5" width="97.54296875" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="27.1328125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.75">
       <c r="A1" s="2" t="s">
         <v>541</v>
       </c>
@@ -10409,7 +10366,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -10429,7 +10386,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -10449,7 +10406,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -10469,7 +10426,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -10489,7 +10446,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -10509,7 +10466,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -10529,7 +10486,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A8" s="1" t="s">
         <v>5</v>
       </c>
@@ -10549,7 +10506,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A9" s="1" t="s">
         <v>5</v>
       </c>
@@ -10569,7 +10526,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A10" s="1" t="s">
         <v>5</v>
       </c>
@@ -10589,7 +10546,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A11" s="1" t="s">
         <v>5</v>
       </c>
@@ -10609,7 +10566,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A12" s="1" t="s">
         <v>5</v>
       </c>
@@ -10629,7 +10586,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A13" s="1" t="s">
         <v>5</v>
       </c>
@@ -10649,7 +10606,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A14" s="1" t="s">
         <v>5</v>
       </c>
@@ -10669,7 +10626,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A15" s="1" t="s">
         <v>5</v>
       </c>
@@ -10689,7 +10646,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A16" s="1" t="s">
         <v>5</v>
       </c>
@@ -10709,7 +10666,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A17" s="1" t="s">
         <v>5</v>
       </c>
@@ -10729,7 +10686,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A18" s="1" t="s">
         <v>5</v>
       </c>
@@ -10749,7 +10706,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A19" s="1" t="s">
         <v>5</v>
       </c>
@@ -10769,7 +10726,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A20" s="1" t="s">
         <v>5</v>
       </c>
@@ -10789,7 +10746,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A21" s="1" t="s">
         <v>5</v>
       </c>
@@ -10809,7 +10766,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A22" s="1" t="s">
         <v>5</v>
       </c>
@@ -10829,7 +10786,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A23" s="1" t="s">
         <v>5</v>
       </c>
@@ -10849,7 +10806,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A24" s="1" t="s">
         <v>5</v>
       </c>
@@ -10869,7 +10826,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A25" s="1" t="s">
         <v>5</v>
       </c>
@@ -10889,7 +10846,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A26" s="1" t="s">
         <v>5</v>
       </c>
@@ -10909,7 +10866,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A27" s="1" t="s">
         <v>5</v>
       </c>
@@ -10929,7 +10886,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A28" s="1" t="s">
         <v>5</v>
       </c>
@@ -10949,7 +10906,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A29" s="1" t="s">
         <v>5</v>
       </c>
@@ -10969,7 +10926,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A30" s="1" t="s">
         <v>5</v>
       </c>
@@ -10989,7 +10946,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A31" s="1" t="s">
         <v>5</v>
       </c>
@@ -11009,7 +10966,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A32" s="1" t="s">
         <v>5</v>
       </c>
@@ -11029,7 +10986,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A33" s="1" t="s">
         <v>5</v>
       </c>
@@ -11049,7 +11006,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A34" s="1" t="s">
         <v>5</v>
       </c>
@@ -11069,7 +11026,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A35" s="1" t="s">
         <v>5</v>
       </c>
@@ -11089,7 +11046,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A36" s="1" t="s">
         <v>5</v>
       </c>
@@ -11109,7 +11066,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A37" s="1" t="s">
         <v>5</v>
       </c>
@@ -11129,7 +11086,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A38" s="1" t="s">
         <v>5</v>
       </c>
@@ -11149,7 +11106,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A39" s="1" t="s">
         <v>5</v>
       </c>
@@ -11169,7 +11126,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A40" s="1" t="s">
         <v>5</v>
       </c>
@@ -11189,7 +11146,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A41" s="1" t="s">
         <v>5</v>
       </c>
@@ -11209,7 +11166,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A42" s="1" t="s">
         <v>5</v>
       </c>
@@ -11229,7 +11186,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A43" s="1" t="s">
         <v>5</v>
       </c>
@@ -11249,7 +11206,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A44" s="1" t="s">
         <v>5</v>
       </c>
@@ -11269,7 +11226,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A45" s="1" t="s">
         <v>5</v>
       </c>
@@ -11289,7 +11246,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A46" s="1" t="s">
         <v>5</v>
       </c>
@@ -11309,7 +11266,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A47" s="1" t="s">
         <v>5</v>
       </c>
@@ -11329,7 +11286,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A48" s="1" t="s">
         <v>5</v>
       </c>
@@ -11349,7 +11306,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A49" s="1" t="s">
         <v>5</v>
       </c>
@@ -11369,7 +11326,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A50" s="1" t="s">
         <v>5</v>
       </c>
@@ -11389,7 +11346,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A51" s="1" t="s">
         <v>5</v>
       </c>
@@ -11409,7 +11366,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A52" s="1" t="s">
         <v>5</v>
       </c>
@@ -11429,7 +11386,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A53" s="1" t="s">
         <v>5</v>
       </c>
@@ -11449,7 +11406,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A54" s="1" t="s">
         <v>5</v>
       </c>
@@ -11469,7 +11426,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A55" s="1" t="s">
         <v>5</v>
       </c>
@@ -11489,7 +11446,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A56" s="1" t="s">
         <v>5</v>
       </c>
@@ -11509,7 +11466,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A57" s="1" t="s">
         <v>5</v>
       </c>
@@ -11529,7 +11486,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A58" s="1" t="s">
         <v>5</v>
       </c>
@@ -11549,7 +11506,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A59" s="1" t="s">
         <v>5</v>
       </c>
@@ -11569,7 +11526,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A60" s="1" t="s">
         <v>5</v>
       </c>
@@ -11589,7 +11546,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A61" s="1" t="s">
         <v>5</v>
       </c>
@@ -11609,7 +11566,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A62" s="1" t="s">
         <v>5</v>
       </c>
@@ -11629,7 +11586,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A63" s="1" t="s">
         <v>5</v>
       </c>
@@ -11649,7 +11606,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A64" s="1" t="s">
         <v>5</v>
       </c>
@@ -11669,7 +11626,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A65" s="1" t="s">
         <v>5</v>
       </c>
@@ -11689,7 +11646,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A66" s="1" t="s">
         <v>5</v>
       </c>
@@ -11709,7 +11666,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A67" s="1" t="s">
         <v>5</v>
       </c>
@@ -11729,7 +11686,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A68" s="1" t="s">
         <v>5</v>
       </c>
@@ -11749,7 +11706,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A69" s="1" t="s">
         <v>5</v>
       </c>
@@ -11769,7 +11726,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A70" s="1" t="s">
         <v>5</v>
       </c>
@@ -11789,7 +11746,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A71" s="1" t="s">
         <v>5</v>
       </c>
@@ -11809,7 +11766,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A72" s="1" t="s">
         <v>5</v>
       </c>
@@ -11829,7 +11786,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A73" s="1" t="s">
         <v>5</v>
       </c>
@@ -11849,7 +11806,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A74" s="1" t="s">
         <v>5</v>
       </c>
@@ -11869,7 +11826,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A75" s="1" t="s">
         <v>5</v>
       </c>
@@ -11889,7 +11846,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A76" s="1" t="s">
         <v>5</v>
       </c>
@@ -11909,7 +11866,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A77" s="1" t="s">
         <v>5</v>
       </c>
@@ -11929,7 +11886,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A78" s="1" t="s">
         <v>5</v>
       </c>
@@ -11949,7 +11906,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A79" s="1" t="s">
         <v>5</v>
       </c>
@@ -11969,7 +11926,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A80" s="1" t="s">
         <v>5</v>
       </c>
@@ -11989,7 +11946,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A81" s="1" t="s">
         <v>5</v>
       </c>
@@ -12009,7 +11966,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A82" s="1" t="s">
         <v>5</v>
       </c>
@@ -12029,7 +11986,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A83" s="1" t="s">
         <v>5</v>
       </c>
@@ -12049,7 +12006,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A84" s="1" t="s">
         <v>5</v>
       </c>
@@ -12069,7 +12026,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A85" s="1" t="s">
         <v>5</v>
       </c>
@@ -12089,7 +12046,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A86" s="1" t="s">
         <v>5</v>
       </c>
@@ -12109,7 +12066,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A87" s="1" t="s">
         <v>5</v>
       </c>
@@ -12129,7 +12086,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A88" s="1" t="s">
         <v>5</v>
       </c>
@@ -12149,7 +12106,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A89" s="1" t="s">
         <v>5</v>
       </c>
@@ -12169,7 +12126,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A90" s="1" t="s">
         <v>5</v>
       </c>
@@ -12189,7 +12146,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A91" s="1" t="s">
         <v>5</v>
       </c>
@@ -12209,7 +12166,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A92" s="1" t="s">
         <v>5</v>
       </c>
@@ -12229,7 +12186,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A93" s="1" t="s">
         <v>5</v>
       </c>
@@ -12249,7 +12206,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A94" s="1" t="s">
         <v>5</v>
       </c>
@@ -12269,7 +12226,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A95" s="1" t="s">
         <v>5</v>
       </c>
@@ -12289,7 +12246,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A96" s="1" t="s">
         <v>5</v>
       </c>
@@ -12309,7 +12266,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A97" s="1" t="s">
         <v>5</v>
       </c>
@@ -12329,7 +12286,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A98" s="1" t="s">
         <v>5</v>
       </c>
@@ -12349,7 +12306,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A99" s="1" t="s">
         <v>5</v>
       </c>
@@ -12369,7 +12326,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A100" s="1" t="s">
         <v>5</v>
       </c>
@@ -12389,7 +12346,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A101" s="1" t="s">
         <v>5</v>
       </c>
@@ -12409,7 +12366,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A102" s="1" t="s">
         <v>5</v>
       </c>
@@ -12429,7 +12386,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A103" s="1" t="s">
         <v>5</v>
       </c>
@@ -12449,7 +12406,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A104" s="1" t="s">
         <v>5</v>
       </c>
@@ -12469,7 +12426,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A105" s="1" t="s">
         <v>5</v>
       </c>
@@ -12489,7 +12446,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A106" s="1" t="s">
         <v>5</v>
       </c>
@@ -12509,7 +12466,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A107" s="1" t="s">
         <v>5</v>
       </c>
@@ -12529,7 +12486,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A108" s="1" t="s">
         <v>5</v>
       </c>
@@ -12549,7 +12506,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A109" s="1" t="s">
         <v>5</v>
       </c>
@@ -12569,7 +12526,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A110" s="1" t="s">
         <v>5</v>
       </c>
@@ -12589,7 +12546,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A111" s="1" t="s">
         <v>5</v>
       </c>
@@ -12609,7 +12566,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A112" s="1" t="s">
         <v>5</v>
       </c>
@@ -12629,7 +12586,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A113" s="1" t="s">
         <v>5</v>
       </c>
@@ -12649,7 +12606,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A114" s="1" t="s">
         <v>5</v>
       </c>
@@ -12669,7 +12626,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A115" s="1" t="s">
         <v>5</v>
       </c>
@@ -12689,7 +12646,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A116" s="1" t="s">
         <v>5</v>
       </c>
@@ -12709,7 +12666,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A117" s="1" t="s">
         <v>5</v>
       </c>
@@ -12729,7 +12686,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A118" s="1" t="s">
         <v>5</v>
       </c>
@@ -12749,7 +12706,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A119" s="1" t="s">
         <v>5</v>
       </c>
@@ -12769,7 +12726,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A120" s="1" t="s">
         <v>5</v>
       </c>
@@ -12789,7 +12746,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A121" s="1" t="s">
         <v>5</v>
       </c>
@@ -12809,7 +12766,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A122" s="1" t="s">
         <v>5</v>
       </c>
@@ -12829,7 +12786,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A123" s="1" t="s">
         <v>5</v>
       </c>
@@ -12849,7 +12806,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A124" s="1" t="s">
         <v>5</v>
       </c>
@@ -12869,7 +12826,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A125" s="1" t="s">
         <v>5</v>
       </c>
@@ -12889,7 +12846,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A126" s="1" t="s">
         <v>5</v>
       </c>
@@ -12909,7 +12866,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A127" s="1" t="s">
         <v>5</v>
       </c>
@@ -12929,7 +12886,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A128" s="1" t="s">
         <v>5</v>
       </c>
@@ -12949,7 +12906,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A129" s="1" t="s">
         <v>5</v>
       </c>
@@ -12969,7 +12926,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A130" s="1" t="s">
         <v>5</v>
       </c>
@@ -12989,7 +12946,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A131" s="1" t="s">
         <v>5</v>
       </c>
@@ -13009,7 +12966,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A132" s="1" t="s">
         <v>5</v>
       </c>
@@ -13029,7 +12986,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A133" s="1" t="s">
         <v>5</v>
       </c>
@@ -13049,7 +13006,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A134" s="1" t="s">
         <v>5</v>
       </c>
@@ -13069,7 +13026,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A135" s="1" t="s">
         <v>5</v>
       </c>
@@ -13089,7 +13046,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A136" s="1" t="s">
         <v>5</v>
       </c>
@@ -13109,7 +13066,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A137" s="1" t="s">
         <v>5</v>
       </c>
@@ -13129,7 +13086,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A138" s="1" t="s">
         <v>5</v>
       </c>
@@ -13149,7 +13106,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A139" s="1" t="s">
         <v>5</v>
       </c>
@@ -13169,7 +13126,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A140" s="1" t="s">
         <v>5</v>
       </c>
@@ -13189,7 +13146,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A141" s="1" t="s">
         <v>5</v>
       </c>
@@ -13209,7 +13166,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A142" s="1" t="s">
         <v>5</v>
       </c>
@@ -13229,7 +13186,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A143" s="1" t="s">
         <v>5</v>
       </c>
@@ -13249,7 +13206,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A144" s="1" t="s">
         <v>5</v>
       </c>
@@ -13269,7 +13226,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A145" s="1" t="s">
         <v>5</v>
       </c>
@@ -13289,7 +13246,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A146" s="1" t="s">
         <v>5</v>
       </c>
@@ -13309,7 +13266,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A147" s="1" t="s">
         <v>5</v>
       </c>
@@ -13329,7 +13286,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A148" s="1" t="s">
         <v>5</v>
       </c>
@@ -13349,7 +13306,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A149" s="1" t="s">
         <v>5</v>
       </c>
@@ -13369,7 +13326,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A150" s="1" t="s">
         <v>5</v>
       </c>
@@ -13389,7 +13346,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A151" s="1" t="s">
         <v>5</v>
       </c>
@@ -13409,7 +13366,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A152" s="1" t="s">
         <v>5</v>
       </c>
@@ -13429,7 +13386,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A153" s="1" t="s">
         <v>5</v>
       </c>
@@ -13449,7 +13406,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A154" s="1" t="s">
         <v>5</v>
       </c>
@@ -13469,7 +13426,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A155" s="1" t="s">
         <v>5</v>
       </c>
@@ -13489,7 +13446,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A156" s="1" t="s">
         <v>5</v>
       </c>
@@ -13509,7 +13466,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A157" s="1" t="s">
         <v>5</v>
       </c>
@@ -13529,7 +13486,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A158" s="1" t="s">
         <v>5</v>
       </c>
@@ -13549,7 +13506,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A159" s="1" t="s">
         <v>5</v>
       </c>
@@ -13569,7 +13526,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A160" s="1" t="s">
         <v>5</v>
       </c>
@@ -13589,7 +13546,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A161" s="1" t="s">
         <v>5</v>
       </c>
@@ -13609,7 +13566,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A162" s="1" t="s">
         <v>5</v>
       </c>
@@ -13629,7 +13586,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A163" s="1" t="s">
         <v>5</v>
       </c>
@@ -13649,7 +13606,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A164" s="1" t="s">
         <v>5</v>
       </c>
@@ -13669,7 +13626,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A165" s="1" t="s">
         <v>5</v>
       </c>
@@ -13689,7 +13646,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A166" s="1" t="s">
         <v>5</v>
       </c>
@@ -13709,7 +13666,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A167" s="1" t="s">
         <v>5</v>
       </c>
@@ -13729,7 +13686,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A168" s="1" t="s">
         <v>5</v>
       </c>
@@ -13749,7 +13706,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A169" s="1" t="s">
         <v>5</v>
       </c>
@@ -13769,7 +13726,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A170" s="1" t="s">
         <v>5</v>
       </c>
@@ -13789,7 +13746,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A171" s="1" t="s">
         <v>5</v>
       </c>
@@ -13809,7 +13766,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A172" s="1" t="s">
         <v>5</v>
       </c>
@@ -13829,7 +13786,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A173" s="1" t="s">
         <v>5</v>
       </c>
@@ -13849,7 +13806,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A174" s="1" t="s">
         <v>5</v>
       </c>
@@ -13869,7 +13826,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A175" s="1" t="s">
         <v>5</v>
       </c>
@@ -13889,7 +13846,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A176" s="1" t="s">
         <v>5</v>
       </c>
@@ -13909,7 +13866,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A177" s="1" t="s">
         <v>5</v>
       </c>
@@ -13929,7 +13886,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A178" s="1" t="s">
         <v>5</v>
       </c>
@@ -13949,7 +13906,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A179" s="1" t="s">
         <v>5</v>
       </c>
@@ -13969,7 +13926,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A180" s="1" t="s">
         <v>5</v>
       </c>
@@ -13989,7 +13946,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A181" s="1" t="s">
         <v>5</v>
       </c>
@@ -14009,7 +13966,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A182" s="1" t="s">
         <v>5</v>
       </c>
@@ -14029,7 +13986,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A183" s="1" t="s">
         <v>5</v>
       </c>
@@ -14049,7 +14006,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A184" s="1" t="s">
         <v>5</v>
       </c>
@@ -14069,7 +14026,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A185" s="1" t="s">
         <v>5</v>
       </c>
@@ -14089,7 +14046,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A186" s="1" t="s">
         <v>5</v>
       </c>
@@ -14109,7 +14066,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A187" s="1" t="s">
         <v>5</v>
       </c>
@@ -14129,7 +14086,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A188" s="1" t="s">
         <v>5</v>
       </c>
@@ -14149,7 +14106,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A189" s="1" t="s">
         <v>5</v>
       </c>
@@ -14169,7 +14126,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A190" s="1" t="s">
         <v>5</v>
       </c>
@@ -14189,7 +14146,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A191" s="1" t="s">
         <v>5</v>
       </c>
@@ -14209,7 +14166,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A192" s="1" t="s">
         <v>5</v>
       </c>
@@ -14229,7 +14186,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A193" s="1" t="s">
         <v>5</v>
       </c>
@@ -14249,7 +14206,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A194" s="1" t="s">
         <v>5</v>
       </c>
@@ -14269,7 +14226,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A195" s="1" t="s">
         <v>5</v>
       </c>
@@ -14289,7 +14246,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A196" s="1" t="s">
         <v>5</v>
       </c>
@@ -14309,7 +14266,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A197" s="1" t="s">
         <v>5</v>
       </c>
@@ -14329,7 +14286,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A198" s="1" t="s">
         <v>5</v>
       </c>
@@ -14349,7 +14306,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A199" s="1" t="s">
         <v>5</v>
       </c>
@@ -14369,7 +14326,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A200" s="1" t="s">
         <v>5</v>
       </c>
@@ -14389,7 +14346,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A201" s="1" t="s">
         <v>5</v>
       </c>
@@ -14409,7 +14366,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A202" s="1" t="s">
         <v>5</v>
       </c>
@@ -14429,7 +14386,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A203" s="1" t="s">
         <v>5</v>
       </c>
@@ -14449,7 +14406,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A204" s="1" t="s">
         <v>5</v>
       </c>
@@ -14469,7 +14426,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A205" s="1" t="s">
         <v>5</v>
       </c>
@@ -14489,7 +14446,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A206" s="1" t="s">
         <v>5</v>
       </c>
@@ -14509,7 +14466,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A207" s="1" t="s">
         <v>5</v>
       </c>
@@ -14529,7 +14486,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A208" s="1" t="s">
         <v>5</v>
       </c>
@@ -14549,7 +14506,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A209" s="1" t="s">
         <v>5</v>
       </c>
@@ -14569,7 +14526,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A210" s="1" t="s">
         <v>5</v>
       </c>
@@ -14589,7 +14546,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A211" s="1" t="s">
         <v>5</v>
       </c>
@@ -14609,7 +14566,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A212" s="1" t="s">
         <v>5</v>
       </c>
@@ -14629,7 +14586,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A213" s="1" t="s">
         <v>5</v>
       </c>
@@ -14649,7 +14606,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A214" s="1" t="s">
         <v>5</v>
       </c>
@@ -14669,7 +14626,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A215" s="1" t="s">
         <v>5</v>
       </c>
@@ -14689,7 +14646,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A216" s="1" t="s">
         <v>5</v>
       </c>
@@ -14709,7 +14666,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A217" s="1" t="s">
         <v>5</v>
       </c>
@@ -14729,7 +14686,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A218" s="1" t="s">
         <v>5</v>
       </c>
@@ -14749,7 +14706,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A219" s="1" t="s">
         <v>5</v>
       </c>
@@ -14769,7 +14726,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A220" s="1" t="s">
         <v>5</v>
       </c>
@@ -14789,7 +14746,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A221" s="1" t="s">
         <v>5</v>
       </c>
@@ -14809,7 +14766,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A222" s="1" t="s">
         <v>5</v>
       </c>
@@ -14829,7 +14786,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A223" s="1" t="s">
         <v>5</v>
       </c>
@@ -14849,7 +14806,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A224" s="1" t="s">
         <v>5</v>
       </c>
@@ -14869,7 +14826,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A225" s="1" t="s">
         <v>5</v>
       </c>
@@ -14889,7 +14846,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A226" s="1" t="s">
         <v>5</v>
       </c>
@@ -14909,7 +14866,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A227" s="1" t="s">
         <v>5</v>
       </c>
@@ -14929,7 +14886,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A228" s="1" t="s">
         <v>5</v>
       </c>
@@ -14949,7 +14906,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A229" s="1" t="s">
         <v>5</v>
       </c>
@@ -14969,7 +14926,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A230" s="1" t="s">
         <v>5</v>
       </c>
@@ -14989,7 +14946,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A231" s="1" t="s">
         <v>5</v>
       </c>
@@ -15009,7 +14966,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A232" s="1" t="s">
         <v>5</v>
       </c>
@@ -15029,7 +14986,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A233" s="1" t="s">
         <v>5</v>
       </c>
@@ -15049,7 +15006,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A234" s="1" t="s">
         <v>5</v>
       </c>
@@ -15069,7 +15026,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A235" s="1" t="s">
         <v>5</v>
       </c>
@@ -15089,7 +15046,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A236" s="1" t="s">
         <v>5</v>
       </c>
@@ -15109,7 +15066,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A237" s="1" t="s">
         <v>5</v>
       </c>
@@ -15129,7 +15086,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A238" s="1" t="s">
         <v>5</v>
       </c>
@@ -15149,7 +15106,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A239" s="1" t="s">
         <v>5</v>
       </c>
@@ -15169,7 +15126,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A240" s="1" t="s">
         <v>5</v>
       </c>
@@ -15189,7 +15146,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A241" s="1" t="s">
         <v>5</v>
       </c>
@@ -15209,7 +15166,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A242" s="1" t="s">
         <v>5</v>
       </c>
@@ -15229,7 +15186,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A243" s="1" t="s">
         <v>5</v>
       </c>
@@ -15249,7 +15206,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A244" s="1" t="s">
         <v>5</v>
       </c>
@@ -15269,7 +15226,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A245" s="1" t="s">
         <v>5</v>
       </c>
@@ -15289,7 +15246,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A246" s="1" t="s">
         <v>5</v>
       </c>
@@ -15309,7 +15266,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A247" s="1" t="s">
         <v>5</v>
       </c>
@@ -15329,7 +15286,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A248" s="1" t="s">
         <v>5</v>
       </c>
@@ -15349,7 +15306,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A249" s="1" t="s">
         <v>5</v>
       </c>
@@ -15369,7 +15326,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A250" s="1" t="s">
         <v>5</v>
       </c>
@@ -15389,7 +15346,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A251" s="1" t="s">
         <v>5</v>
       </c>
@@ -15409,7 +15366,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A252" s="1" t="s">
         <v>5</v>
       </c>
@@ -15429,7 +15386,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A253" s="1" t="s">
         <v>5</v>
       </c>
@@ -15449,7 +15406,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A254" s="1" t="s">
         <v>5</v>
       </c>
@@ -15469,7 +15426,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A255" s="1" t="s">
         <v>5</v>
       </c>
@@ -15489,7 +15446,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A256" s="1" t="s">
         <v>5</v>
       </c>
@@ -15509,7 +15466,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A257" s="1" t="s">
         <v>5</v>
       </c>
@@ -15529,7 +15486,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A258" s="1" t="s">
         <v>5</v>
       </c>
@@ -15549,7 +15506,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A259" s="1" t="s">
         <v>5</v>
       </c>
@@ -15569,7 +15526,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A260" s="1" t="s">
         <v>5</v>
       </c>
@@ -15589,7 +15546,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A261" s="1" t="s">
         <v>5</v>
       </c>
@@ -15609,7 +15566,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A262" s="1" t="s">
         <v>5</v>
       </c>
@@ -15629,7 +15586,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A263" s="1" t="s">
         <v>5</v>
       </c>
@@ -15649,7 +15606,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A264" s="1" t="s">
         <v>5</v>
       </c>
@@ -15669,7 +15626,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A265" s="1" t="s">
         <v>5</v>
       </c>
@@ -15689,7 +15646,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A266" s="1" t="s">
         <v>5</v>
       </c>
@@ -15709,7 +15666,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A267" s="1" t="s">
         <v>5</v>
       </c>
@@ -15729,7 +15686,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A268" s="1" t="s">
         <v>5</v>
       </c>
@@ -15749,7 +15706,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A269" s="1" t="s">
         <v>5</v>
       </c>
@@ -15777,17 +15734,17 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:F179"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="15" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="15" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="4.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.42578125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="46.42578125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="43.28515625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="156.42578125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="4.26953125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.40625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="46.40625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="43.26953125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="156.40625" style="1" customWidth="1"/>
     <col min="6" max="16384" width="15" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.75">
       <c r="A1" s="2" t="s">
         <v>541</v>
       </c>
@@ -15807,7 +15764,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -15827,7 +15784,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -15847,7 +15804,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -15867,7 +15824,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -15887,7 +15844,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -15907,7 +15864,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -15927,7 +15884,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A8" s="1" t="s">
         <v>5</v>
       </c>
@@ -15947,7 +15904,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A9" s="1" t="s">
         <v>5</v>
       </c>
@@ -15967,7 +15924,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A10" s="1" t="s">
         <v>5</v>
       </c>
@@ -15987,7 +15944,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A11" s="1" t="s">
         <v>5</v>
       </c>
@@ -16007,7 +15964,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A12" s="1" t="s">
         <v>5</v>
       </c>
@@ -16027,7 +15984,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A13" s="1" t="s">
         <v>5</v>
       </c>
@@ -16047,7 +16004,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A14" s="1" t="s">
         <v>5</v>
       </c>
@@ -16067,7 +16024,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A15" s="1" t="s">
         <v>5</v>
       </c>
@@ -16087,7 +16044,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A16" s="1" t="s">
         <v>5</v>
       </c>
@@ -16107,7 +16064,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A17" s="1" t="s">
         <v>5</v>
       </c>
@@ -16127,7 +16084,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A18" s="1" t="s">
         <v>5</v>
       </c>
@@ -16147,7 +16104,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A19" s="1" t="s">
         <v>5</v>
       </c>
@@ -16167,7 +16124,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A20" s="1" t="s">
         <v>5</v>
       </c>
@@ -16187,7 +16144,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A21" s="1" t="s">
         <v>5</v>
       </c>
@@ -16207,7 +16164,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A22" s="1" t="s">
         <v>5</v>
       </c>
@@ -16227,7 +16184,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A23" s="1" t="s">
         <v>5</v>
       </c>
@@ -16247,7 +16204,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A24" s="1" t="s">
         <v>5</v>
       </c>
@@ -16267,7 +16224,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A25" s="1" t="s">
         <v>5</v>
       </c>
@@ -16287,7 +16244,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A26" s="1" t="s">
         <v>5</v>
       </c>
@@ -16307,7 +16264,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A27" s="1" t="s">
         <v>5</v>
       </c>
@@ -16327,7 +16284,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A28" s="1" t="s">
         <v>5</v>
       </c>
@@ -16347,7 +16304,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A29" s="1" t="s">
         <v>5</v>
       </c>
@@ -16367,7 +16324,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A30" s="1" t="s">
         <v>5</v>
       </c>
@@ -16387,7 +16344,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A31" s="1" t="s">
         <v>5</v>
       </c>
@@ -16407,7 +16364,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A32" s="1" t="s">
         <v>5</v>
       </c>
@@ -16427,7 +16384,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A33" s="1" t="s">
         <v>5</v>
       </c>
@@ -16447,7 +16404,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A34" s="1" t="s">
         <v>5</v>
       </c>
@@ -16467,7 +16424,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A35" s="1" t="s">
         <v>5</v>
       </c>
@@ -16487,7 +16444,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A36" s="1" t="s">
         <v>5</v>
       </c>
@@ -16507,7 +16464,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A37" s="1" t="s">
         <v>5</v>
       </c>
@@ -16527,7 +16484,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A38" s="1" t="s">
         <v>5</v>
       </c>
@@ -16547,7 +16504,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A39" s="1" t="s">
         <v>5</v>
       </c>
@@ -16567,7 +16524,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A40" s="1" t="s">
         <v>5</v>
       </c>
@@ -16587,7 +16544,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A41" s="1" t="s">
         <v>5</v>
       </c>
@@ -16607,7 +16564,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A42" s="1" t="s">
         <v>5</v>
       </c>
@@ -16627,7 +16584,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A43" s="1" t="s">
         <v>5</v>
       </c>
@@ -16647,7 +16604,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A44" s="1" t="s">
         <v>5</v>
       </c>
@@ -16667,7 +16624,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A45" s="1" t="s">
         <v>5</v>
       </c>
@@ -16687,7 +16644,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A46" s="1" t="s">
         <v>5</v>
       </c>
@@ -16707,7 +16664,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A47" s="1" t="s">
         <v>5</v>
       </c>
@@ -16727,7 +16684,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A48" s="1" t="s">
         <v>5</v>
       </c>
@@ -16747,7 +16704,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A49" s="1" t="s">
         <v>5</v>
       </c>
@@ -16767,7 +16724,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A50" s="1" t="s">
         <v>5</v>
       </c>
@@ -16787,7 +16744,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A51" s="1" t="s">
         <v>5</v>
       </c>
@@ -16807,7 +16764,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A52" s="1" t="s">
         <v>5</v>
       </c>
@@ -16827,7 +16784,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A53" s="1" t="s">
         <v>5</v>
       </c>
@@ -16847,7 +16804,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A54" s="1" t="s">
         <v>5</v>
       </c>
@@ -16867,7 +16824,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A55" s="1" t="s">
         <v>5</v>
       </c>
@@ -16887,7 +16844,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A56" s="1" t="s">
         <v>5</v>
       </c>
@@ -16907,7 +16864,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A57" s="1" t="s">
         <v>5</v>
       </c>
@@ -16927,7 +16884,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A58" s="1" t="s">
         <v>5</v>
       </c>
@@ -16947,7 +16904,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A59" s="1" t="s">
         <v>5</v>
       </c>
@@ -16967,7 +16924,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A60" s="1" t="s">
         <v>5</v>
       </c>
@@ -16987,7 +16944,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A61" s="1" t="s">
         <v>5</v>
       </c>
@@ -17007,7 +16964,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A62" s="1" t="s">
         <v>5</v>
       </c>
@@ -17027,7 +16984,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A63" s="1" t="s">
         <v>5</v>
       </c>
@@ -17047,7 +17004,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A64" s="1" t="s">
         <v>5</v>
       </c>
@@ -17067,7 +17024,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A65" s="1" t="s">
         <v>5</v>
       </c>
@@ -17087,7 +17044,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A66" s="1" t="s">
         <v>5</v>
       </c>
@@ -17107,7 +17064,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A67" s="1" t="s">
         <v>5</v>
       </c>
@@ -17127,7 +17084,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A68" s="1" t="s">
         <v>5</v>
       </c>
@@ -17147,7 +17104,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A69" s="1" t="s">
         <v>5</v>
       </c>
@@ -17167,7 +17124,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A70" s="1" t="s">
         <v>5</v>
       </c>
@@ -17187,7 +17144,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A71" s="1" t="s">
         <v>5</v>
       </c>
@@ -17207,7 +17164,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A72" s="1" t="s">
         <v>5</v>
       </c>
@@ -17227,7 +17184,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A73" s="1" t="s">
         <v>5</v>
       </c>
@@ -17247,7 +17204,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A74" s="1" t="s">
         <v>5</v>
       </c>
@@ -17267,7 +17224,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A75" s="1" t="s">
         <v>5</v>
       </c>
@@ -17287,7 +17244,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A76" s="1" t="s">
         <v>5</v>
       </c>
@@ -17307,7 +17264,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A77" s="1" t="s">
         <v>5</v>
       </c>
@@ -17327,7 +17284,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A78" s="1" t="s">
         <v>5</v>
       </c>
@@ -17347,7 +17304,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A79" s="1" t="s">
         <v>5</v>
       </c>
@@ -17367,7 +17324,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A80" s="1" t="s">
         <v>5</v>
       </c>
@@ -17387,7 +17344,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A81" s="1" t="s">
         <v>5</v>
       </c>
@@ -17407,7 +17364,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A82" s="1" t="s">
         <v>5</v>
       </c>
@@ -17427,7 +17384,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A83" s="1" t="s">
         <v>5</v>
       </c>
@@ -17447,7 +17404,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A84" s="1" t="s">
         <v>5</v>
       </c>
@@ -17467,7 +17424,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A85" s="1" t="s">
         <v>5</v>
       </c>
@@ -17487,7 +17444,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A86" s="1" t="s">
         <v>5</v>
       </c>
@@ -17507,7 +17464,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A87" s="1" t="s">
         <v>5</v>
       </c>
@@ -17527,7 +17484,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A88" s="1" t="s">
         <v>5</v>
       </c>
@@ -17547,7 +17504,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A89" s="1" t="s">
         <v>5</v>
       </c>
@@ -17567,7 +17524,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A90" s="1" t="s">
         <v>5</v>
       </c>
@@ -17587,7 +17544,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A91" s="1" t="s">
         <v>5</v>
       </c>
@@ -17607,7 +17564,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A92" s="1" t="s">
         <v>5</v>
       </c>
@@ -17627,7 +17584,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A93" s="1" t="s">
         <v>5</v>
       </c>
@@ -17647,7 +17604,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A94" s="1" t="s">
         <v>5</v>
       </c>
@@ -17667,7 +17624,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A95" s="1" t="s">
         <v>5</v>
       </c>
@@ -17687,7 +17644,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A96" s="1" t="s">
         <v>5</v>
       </c>
@@ -17707,7 +17664,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A97" s="1" t="s">
         <v>5</v>
       </c>
@@ -17727,7 +17684,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A98" s="1" t="s">
         <v>5</v>
       </c>
@@ -17747,7 +17704,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A99" s="1" t="s">
         <v>5</v>
       </c>
@@ -17767,7 +17724,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A100" s="1" t="s">
         <v>5</v>
       </c>
@@ -17787,7 +17744,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A101" s="1" t="s">
         <v>5</v>
       </c>
@@ -17807,7 +17764,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A102" s="1" t="s">
         <v>5</v>
       </c>
@@ -17827,7 +17784,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A103" s="1" t="s">
         <v>5</v>
       </c>
@@ -17847,7 +17804,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A104" s="1" t="s">
         <v>5</v>
       </c>
@@ -17867,7 +17824,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A105" s="1" t="s">
         <v>5</v>
       </c>
@@ -17887,7 +17844,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A106" s="1" t="s">
         <v>5</v>
       </c>
@@ -17907,7 +17864,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A107" s="1" t="s">
         <v>5</v>
       </c>
@@ -17927,7 +17884,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A108" s="1" t="s">
         <v>5</v>
       </c>
@@ -17947,7 +17904,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A109" s="1" t="s">
         <v>5</v>
       </c>
@@ -17967,7 +17924,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A110" s="1" t="s">
         <v>5</v>
       </c>
@@ -17987,7 +17944,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A111" s="1" t="s">
         <v>5</v>
       </c>
@@ -18007,7 +17964,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A112" s="1" t="s">
         <v>5</v>
       </c>
@@ -18027,7 +17984,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A113" s="1" t="s">
         <v>5</v>
       </c>
@@ -18047,7 +18004,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A114" s="1" t="s">
         <v>5</v>
       </c>
@@ -18067,7 +18024,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A115" s="1" t="s">
         <v>5</v>
       </c>
@@ -18087,7 +18044,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A116" s="1" t="s">
         <v>5</v>
       </c>
@@ -18107,7 +18064,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A117" s="1" t="s">
         <v>5</v>
       </c>
@@ -18127,7 +18084,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A118" s="1" t="s">
         <v>5</v>
       </c>
@@ -18147,7 +18104,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A119" s="1" t="s">
         <v>5</v>
       </c>
@@ -18167,7 +18124,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A120" s="1" t="s">
         <v>5</v>
       </c>
@@ -18187,7 +18144,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A121" s="1" t="s">
         <v>5</v>
       </c>
@@ -18207,7 +18164,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A122" s="1" t="s">
         <v>5</v>
       </c>
@@ -18227,7 +18184,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A123" s="1" t="s">
         <v>5</v>
       </c>
@@ -18247,7 +18204,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A124" s="1" t="s">
         <v>5</v>
       </c>
@@ -18267,7 +18224,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A125" s="1" t="s">
         <v>5</v>
       </c>
@@ -18287,7 +18244,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A126" s="1" t="s">
         <v>5</v>
       </c>
@@ -18307,7 +18264,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A127" s="1" t="s">
         <v>5</v>
       </c>
@@ -18327,7 +18284,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A128" s="1" t="s">
         <v>5</v>
       </c>
@@ -18347,7 +18304,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A129" s="1" t="s">
         <v>5</v>
       </c>
@@ -18367,7 +18324,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A130" s="1" t="s">
         <v>5</v>
       </c>
@@ -18387,7 +18344,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A131" s="1" t="s">
         <v>5</v>
       </c>
@@ -18407,7 +18364,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A132" s="1" t="s">
         <v>5</v>
       </c>
@@ -18427,7 +18384,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A133" s="1" t="s">
         <v>5</v>
       </c>
@@ -18447,7 +18404,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A134" s="1" t="s">
         <v>5</v>
       </c>
@@ -18467,7 +18424,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A135" s="1" t="s">
         <v>5</v>
       </c>
@@ -18487,7 +18444,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A136" s="1" t="s">
         <v>5</v>
       </c>
@@ -18507,7 +18464,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A137" s="1" t="s">
         <v>5</v>
       </c>
@@ -18527,7 +18484,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A138" s="1" t="s">
         <v>5</v>
       </c>
@@ -18547,7 +18504,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A139" s="1" t="s">
         <v>5</v>
       </c>
@@ -18567,7 +18524,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A140" s="1" t="s">
         <v>5</v>
       </c>
@@ -18587,7 +18544,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A141" s="1" t="s">
         <v>5</v>
       </c>
@@ -18607,7 +18564,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A142" s="1" t="s">
         <v>5</v>
       </c>
@@ -18627,7 +18584,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A143" s="1" t="s">
         <v>5</v>
       </c>
@@ -18647,7 +18604,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A144" s="1" t="s">
         <v>5</v>
       </c>
@@ -18667,7 +18624,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A145" s="1" t="s">
         <v>5</v>
       </c>
@@ -18687,7 +18644,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A146" s="1" t="s">
         <v>5</v>
       </c>
@@ -18707,7 +18664,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A147" s="1" t="s">
         <v>5</v>
       </c>
@@ -18727,7 +18684,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A148" s="1" t="s">
         <v>5</v>
       </c>
@@ -18747,7 +18704,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A149" s="1" t="s">
         <v>5</v>
       </c>
@@ -18767,7 +18724,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A150" s="1" t="s">
         <v>5</v>
       </c>
@@ -18787,7 +18744,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A151" s="1" t="s">
         <v>5</v>
       </c>
@@ -18807,7 +18764,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A152" s="1" t="s">
         <v>5</v>
       </c>
@@ -18827,7 +18784,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A153" s="1" t="s">
         <v>5</v>
       </c>
@@ -18847,7 +18804,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A154" s="1" t="s">
         <v>5</v>
       </c>
@@ -18867,7 +18824,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A155" s="1" t="s">
         <v>5</v>
       </c>
@@ -18887,7 +18844,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A156" s="1" t="s">
         <v>5</v>
       </c>
@@ -18907,7 +18864,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A157" s="1" t="s">
         <v>5</v>
       </c>
@@ -18927,7 +18884,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A158" s="1" t="s">
         <v>5</v>
       </c>
@@ -18947,7 +18904,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A159" s="1" t="s">
         <v>5</v>
       </c>
@@ -18967,7 +18924,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A160" s="1" t="s">
         <v>5</v>
       </c>
@@ -18987,7 +18944,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A161" s="1" t="s">
         <v>5</v>
       </c>
@@ -19007,7 +18964,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A162" s="1" t="s">
         <v>5</v>
       </c>
@@ -19027,7 +18984,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A163" s="1" t="s">
         <v>5</v>
       </c>
@@ -19047,7 +19004,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A164" s="1" t="s">
         <v>5</v>
       </c>
@@ -19067,7 +19024,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A165" s="1" t="s">
         <v>5</v>
       </c>
@@ -19087,7 +19044,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A166" s="1" t="s">
         <v>5</v>
       </c>
@@ -19107,7 +19064,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A167" s="1" t="s">
         <v>5</v>
       </c>
@@ -19127,7 +19084,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A168" s="1" t="s">
         <v>5</v>
       </c>
@@ -19147,7 +19104,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A169" s="1" t="s">
         <v>5</v>
       </c>
@@ -19167,7 +19124,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A170" s="1" t="s">
         <v>5</v>
       </c>
@@ -19187,7 +19144,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A171" s="1" t="s">
         <v>5</v>
       </c>
@@ -19207,7 +19164,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A172" s="1" t="s">
         <v>5</v>
       </c>
@@ -19227,7 +19184,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A173" s="1" t="s">
         <v>5</v>
       </c>
@@ -19247,7 +19204,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A174" s="1" t="s">
         <v>5</v>
       </c>
@@ -19267,7 +19224,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A175" s="1" t="s">
         <v>5</v>
       </c>
@@ -19287,7 +19244,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A176" s="1" t="s">
         <v>5</v>
       </c>
@@ -19307,7 +19264,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A177" s="1" t="s">
         <v>5</v>
       </c>
@@ -19327,7 +19284,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A178" s="1" t="s">
         <v>5</v>
       </c>
@@ -19347,7 +19304,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A179" s="1" t="s">
         <v>5</v>
       </c>
@@ -19375,12 +19332,12 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:F179"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="35.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="35.54296875" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="16384" width="35.5703125" style="1"/>
+    <col min="1" max="16384" width="35.54296875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.75">
       <c r="A1" s="2" t="s">
         <v>541</v>
       </c>
@@ -19400,7 +19357,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -19420,7 +19377,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -19440,7 +19397,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -19460,7 +19417,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -19480,7 +19437,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -19500,7 +19457,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -19520,7 +19477,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A8" s="1" t="s">
         <v>5</v>
       </c>
@@ -19540,7 +19497,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A9" s="1" t="s">
         <v>5</v>
       </c>
@@ -19560,7 +19517,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A10" s="1" t="s">
         <v>5</v>
       </c>
@@ -19580,7 +19537,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A11" s="1" t="s">
         <v>5</v>
       </c>
@@ -19600,7 +19557,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A12" s="1" t="s">
         <v>5</v>
       </c>
@@ -19620,7 +19577,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A13" s="1" t="s">
         <v>5</v>
       </c>
@@ -19640,7 +19597,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A14" s="1" t="s">
         <v>5</v>
       </c>
@@ -19660,7 +19617,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A15" s="1" t="s">
         <v>5</v>
       </c>
@@ -19680,7 +19637,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A16" s="1" t="s">
         <v>5</v>
       </c>
@@ -19700,7 +19657,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A17" s="1" t="s">
         <v>5</v>
       </c>
@@ -19720,7 +19677,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A18" s="1" t="s">
         <v>5</v>
       </c>
@@ -19740,7 +19697,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A19" s="1" t="s">
         <v>5</v>
       </c>
@@ -19760,7 +19717,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A20" s="1" t="s">
         <v>5</v>
       </c>
@@ -19780,7 +19737,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A21" s="1" t="s">
         <v>5</v>
       </c>
@@ -19800,7 +19757,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A22" s="1" t="s">
         <v>5</v>
       </c>
@@ -19820,7 +19777,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A23" s="1" t="s">
         <v>5</v>
       </c>
@@ -19840,7 +19797,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A24" s="1" t="s">
         <v>5</v>
       </c>
@@ -19860,7 +19817,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A25" s="1" t="s">
         <v>5</v>
       </c>
@@ -19880,7 +19837,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A26" s="1" t="s">
         <v>5</v>
       </c>
@@ -19900,7 +19857,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A27" s="1" t="s">
         <v>5</v>
       </c>
@@ -19920,7 +19877,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A28" s="1" t="s">
         <v>5</v>
       </c>
@@ -19940,7 +19897,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A29" s="1" t="s">
         <v>5</v>
       </c>
@@ -19960,7 +19917,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A30" s="1" t="s">
         <v>5</v>
       </c>
@@ -19980,7 +19937,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A31" s="1" t="s">
         <v>5</v>
       </c>
@@ -20000,7 +19957,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A32" s="1" t="s">
         <v>5</v>
       </c>
@@ -20020,7 +19977,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A33" s="1" t="s">
         <v>5</v>
       </c>
@@ -20040,7 +19997,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A34" s="1" t="s">
         <v>5</v>
       </c>
@@ -20060,7 +20017,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A35" s="1" t="s">
         <v>5</v>
       </c>
@@ -20080,7 +20037,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A36" s="1" t="s">
         <v>5</v>
       </c>
@@ -20100,7 +20057,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A37" s="1" t="s">
         <v>5</v>
       </c>
@@ -20120,7 +20077,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A38" s="1" t="s">
         <v>5</v>
       </c>
@@ -20140,7 +20097,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A39" s="1" t="s">
         <v>5</v>
       </c>
@@ -20160,7 +20117,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A40" s="1" t="s">
         <v>5</v>
       </c>
@@ -20180,7 +20137,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A41" s="1" t="s">
         <v>5</v>
       </c>
@@ -20200,7 +20157,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A42" s="1" t="s">
         <v>5</v>
       </c>
@@ -20220,7 +20177,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A43" s="1" t="s">
         <v>5</v>
       </c>
@@ -20240,7 +20197,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A44" s="1" t="s">
         <v>5</v>
       </c>
@@ -20260,7 +20217,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A45" s="1" t="s">
         <v>5</v>
       </c>
@@ -20280,7 +20237,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A46" s="1" t="s">
         <v>5</v>
       </c>
@@ -20300,7 +20257,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A47" s="1" t="s">
         <v>5</v>
       </c>
@@ -20320,7 +20277,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A48" s="1" t="s">
         <v>5</v>
       </c>
@@ -20340,7 +20297,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A49" s="1" t="s">
         <v>5</v>
       </c>
@@ -20360,7 +20317,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A50" s="1" t="s">
         <v>5</v>
       </c>
@@ -20380,7 +20337,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A51" s="1" t="s">
         <v>5</v>
       </c>
@@ -20400,7 +20357,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A52" s="1" t="s">
         <v>5</v>
       </c>
@@ -20420,7 +20377,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A53" s="1" t="s">
         <v>5</v>
       </c>
@@ -20440,7 +20397,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A54" s="1" t="s">
         <v>5</v>
       </c>
@@ -20460,7 +20417,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A55" s="1" t="s">
         <v>5</v>
       </c>
@@ -20480,7 +20437,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A56" s="1" t="s">
         <v>5</v>
       </c>
@@ -20500,7 +20457,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A57" s="1" t="s">
         <v>5</v>
       </c>
@@ -20520,7 +20477,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A58" s="1" t="s">
         <v>5</v>
       </c>
@@ -20540,7 +20497,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A59" s="1" t="s">
         <v>5</v>
       </c>
@@ -20560,7 +20517,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A60" s="1" t="s">
         <v>5</v>
       </c>
@@ -20580,7 +20537,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A61" s="1" t="s">
         <v>5</v>
       </c>
@@ -20600,7 +20557,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A62" s="1" t="s">
         <v>5</v>
       </c>
@@ -20620,7 +20577,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A63" s="1" t="s">
         <v>5</v>
       </c>
@@ -20640,7 +20597,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A64" s="1" t="s">
         <v>5</v>
       </c>
@@ -20660,7 +20617,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A65" s="1" t="s">
         <v>5</v>
       </c>
@@ -20680,7 +20637,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A66" s="1" t="s">
         <v>5</v>
       </c>
@@ -20700,7 +20657,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A67" s="1" t="s">
         <v>5</v>
       </c>
@@ -20720,7 +20677,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A68" s="1" t="s">
         <v>5</v>
       </c>
@@ -20740,7 +20697,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A69" s="1" t="s">
         <v>5</v>
       </c>
@@ -20760,7 +20717,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A70" s="1" t="s">
         <v>5</v>
       </c>
@@ -20780,7 +20737,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A71" s="1" t="s">
         <v>5</v>
       </c>
@@ -20800,7 +20757,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A72" s="1" t="s">
         <v>5</v>
       </c>
@@ -20820,7 +20777,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A73" s="1" t="s">
         <v>5</v>
       </c>
@@ -20840,7 +20797,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A74" s="1" t="s">
         <v>5</v>
       </c>
@@ -20860,7 +20817,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A75" s="1" t="s">
         <v>5</v>
       </c>
@@ -20880,7 +20837,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A76" s="1" t="s">
         <v>5</v>
       </c>
@@ -20900,7 +20857,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A77" s="1" t="s">
         <v>5</v>
       </c>
@@ -20920,7 +20877,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A78" s="1" t="s">
         <v>5</v>
       </c>
@@ -20940,7 +20897,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A79" s="1" t="s">
         <v>5</v>
       </c>
@@ -20960,7 +20917,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A80" s="1" t="s">
         <v>5</v>
       </c>
@@ -20980,7 +20937,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A81" s="1" t="s">
         <v>5</v>
       </c>
@@ -21000,7 +20957,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A82" s="1" t="s">
         <v>5</v>
       </c>
@@ -21020,7 +20977,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A83" s="1" t="s">
         <v>5</v>
       </c>
@@ -21040,7 +20997,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A84" s="1" t="s">
         <v>5</v>
       </c>
@@ -21060,7 +21017,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A85" s="1" t="s">
         <v>5</v>
       </c>
@@ -21080,7 +21037,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A86" s="1" t="s">
         <v>5</v>
       </c>
@@ -21100,7 +21057,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A87" s="1" t="s">
         <v>5</v>
       </c>
@@ -21120,7 +21077,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A88" s="1" t="s">
         <v>5</v>
       </c>
@@ -21140,7 +21097,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A89" s="1" t="s">
         <v>5</v>
       </c>
@@ -21160,7 +21117,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A90" s="1" t="s">
         <v>5</v>
       </c>
@@ -21180,7 +21137,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A91" s="1" t="s">
         <v>5</v>
       </c>
@@ -21200,7 +21157,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A92" s="1" t="s">
         <v>5</v>
       </c>
@@ -21220,7 +21177,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A93" s="1" t="s">
         <v>5</v>
       </c>
@@ -21240,7 +21197,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A94" s="1" t="s">
         <v>5</v>
       </c>
@@ -21260,7 +21217,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A95" s="1" t="s">
         <v>5</v>
       </c>
@@ -21280,7 +21237,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A96" s="1" t="s">
         <v>5</v>
       </c>
@@ -21300,7 +21257,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A97" s="1" t="s">
         <v>5</v>
       </c>
@@ -21320,7 +21277,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A98" s="1" t="s">
         <v>5</v>
       </c>
@@ -21340,7 +21297,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A99" s="1" t="s">
         <v>5</v>
       </c>
@@ -21360,7 +21317,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A100" s="1" t="s">
         <v>5</v>
       </c>
@@ -21380,7 +21337,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A101" s="1" t="s">
         <v>5</v>
       </c>
@@ -21400,7 +21357,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A102" s="1" t="s">
         <v>5</v>
       </c>
@@ -21420,7 +21377,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A103" s="1" t="s">
         <v>5</v>
       </c>
@@ -21440,7 +21397,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A104" s="1" t="s">
         <v>5</v>
       </c>
@@ -21460,7 +21417,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A105" s="1" t="s">
         <v>5</v>
       </c>
@@ -21480,7 +21437,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A106" s="1" t="s">
         <v>5</v>
       </c>
@@ -21500,7 +21457,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A107" s="1" t="s">
         <v>5</v>
       </c>
@@ -21520,7 +21477,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A108" s="1" t="s">
         <v>5</v>
       </c>
@@ -21540,7 +21497,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A109" s="1" t="s">
         <v>5</v>
       </c>
@@ -21560,7 +21517,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A110" s="1" t="s">
         <v>5</v>
       </c>
@@ -21580,7 +21537,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A111" s="1" t="s">
         <v>5</v>
       </c>
@@ -21600,7 +21557,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A112" s="1" t="s">
         <v>5</v>
       </c>
@@ -21620,7 +21577,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A113" s="1" t="s">
         <v>5</v>
       </c>
@@ -21640,7 +21597,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A114" s="1" t="s">
         <v>5</v>
       </c>
@@ -21660,7 +21617,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A115" s="1" t="s">
         <v>5</v>
       </c>
@@ -21680,7 +21637,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A116" s="1" t="s">
         <v>5</v>
       </c>
@@ -21700,7 +21657,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A117" s="1" t="s">
         <v>5</v>
       </c>
@@ -21720,7 +21677,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A118" s="1" t="s">
         <v>5</v>
       </c>
@@ -21740,7 +21697,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A119" s="1" t="s">
         <v>5</v>
       </c>
@@ -21760,7 +21717,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A120" s="1" t="s">
         <v>5</v>
       </c>
@@ -21780,7 +21737,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A121" s="1" t="s">
         <v>5</v>
       </c>
@@ -21800,7 +21757,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A122" s="1" t="s">
         <v>5</v>
       </c>
@@ -21820,7 +21777,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A123" s="1" t="s">
         <v>5</v>
       </c>
@@ -21840,7 +21797,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A124" s="1" t="s">
         <v>5</v>
       </c>
@@ -21860,7 +21817,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A125" s="1" t="s">
         <v>5</v>
       </c>
@@ -21880,7 +21837,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A126" s="1" t="s">
         <v>5</v>
       </c>
@@ -21900,7 +21857,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A127" s="1" t="s">
         <v>5</v>
       </c>
@@ -21920,7 +21877,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A128" s="1" t="s">
         <v>5</v>
       </c>
@@ -21940,7 +21897,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A129" s="1" t="s">
         <v>5</v>
       </c>
@@ -21960,7 +21917,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A130" s="1" t="s">
         <v>5</v>
       </c>
@@ -21980,7 +21937,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A131" s="1" t="s">
         <v>5</v>
       </c>
@@ -22000,7 +21957,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A132" s="1" t="s">
         <v>5</v>
       </c>
@@ -22020,7 +21977,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A133" s="1" t="s">
         <v>5</v>
       </c>
@@ -22040,7 +21997,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A134" s="1" t="s">
         <v>5</v>
       </c>
@@ -22060,7 +22017,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A135" s="1" t="s">
         <v>5</v>
       </c>
@@ -22080,7 +22037,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A136" s="1" t="s">
         <v>5</v>
       </c>
@@ -22100,7 +22057,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A137" s="1" t="s">
         <v>5</v>
       </c>
@@ -22120,7 +22077,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A138" s="1" t="s">
         <v>5</v>
       </c>
@@ -22140,7 +22097,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A139" s="1" t="s">
         <v>5</v>
       </c>
@@ -22160,7 +22117,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A140" s="1" t="s">
         <v>5</v>
       </c>
@@ -22180,7 +22137,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A141" s="1" t="s">
         <v>5</v>
       </c>
@@ -22200,7 +22157,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A142" s="1" t="s">
         <v>5</v>
       </c>
@@ -22220,7 +22177,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A143" s="1" t="s">
         <v>5</v>
       </c>
@@ -22240,7 +22197,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A144" s="1" t="s">
         <v>5</v>
       </c>
@@ -22260,7 +22217,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A145" s="1" t="s">
         <v>5</v>
       </c>
@@ -22280,7 +22237,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A146" s="1" t="s">
         <v>5</v>
       </c>
@@ -22300,7 +22257,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A147" s="1" t="s">
         <v>5</v>
       </c>
@@ -22320,7 +22277,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A148" s="1" t="s">
         <v>5</v>
       </c>
@@ -22340,7 +22297,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A149" s="1" t="s">
         <v>5</v>
       </c>
@@ -22360,7 +22317,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A150" s="1" t="s">
         <v>5</v>
       </c>
@@ -22380,7 +22337,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A151" s="1" t="s">
         <v>5</v>
       </c>
@@ -22400,7 +22357,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A152" s="1" t="s">
         <v>5</v>
       </c>
@@ -22420,7 +22377,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A153" s="1" t="s">
         <v>5</v>
       </c>
@@ -22440,7 +22397,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A154" s="1" t="s">
         <v>5</v>
       </c>
@@ -22460,7 +22417,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A155" s="1" t="s">
         <v>5</v>
       </c>
@@ -22480,7 +22437,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A156" s="1" t="s">
         <v>5</v>
       </c>
@@ -22500,7 +22457,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A157" s="1" t="s">
         <v>5</v>
       </c>
@@ -22520,7 +22477,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A158" s="1" t="s">
         <v>5</v>
       </c>
@@ -22540,7 +22497,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A159" s="1" t="s">
         <v>5</v>
       </c>
@@ -22560,7 +22517,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A160" s="1" t="s">
         <v>5</v>
       </c>
@@ -22580,7 +22537,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A161" s="1" t="s">
         <v>5</v>
       </c>
@@ -22600,7 +22557,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A162" s="1" t="s">
         <v>5</v>
       </c>
@@ -22620,7 +22577,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A163" s="1" t="s">
         <v>5</v>
       </c>
@@ -22640,7 +22597,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A164" s="1" t="s">
         <v>5</v>
       </c>
@@ -22660,7 +22617,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A165" s="1" t="s">
         <v>5</v>
       </c>
@@ -22680,7 +22637,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A166" s="1" t="s">
         <v>5</v>
       </c>
@@ -22700,7 +22657,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A167" s="1" t="s">
         <v>5</v>
       </c>
@@ -22720,7 +22677,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A168" s="1" t="s">
         <v>5</v>
       </c>
@@ -22740,7 +22697,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A169" s="1" t="s">
         <v>5</v>
       </c>
@@ -22760,7 +22717,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A170" s="1" t="s">
         <v>5</v>
       </c>
@@ -22780,7 +22737,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A171" s="1" t="s">
         <v>5</v>
       </c>
@@ -22800,7 +22757,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A172" s="1" t="s">
         <v>5</v>
       </c>
@@ -22820,7 +22777,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A173" s="1" t="s">
         <v>5</v>
       </c>
@@ -22840,7 +22797,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A174" s="1" t="s">
         <v>5</v>
       </c>
@@ -22860,7 +22817,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A175" s="1" t="s">
         <v>5</v>
       </c>
@@ -22880,7 +22837,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A176" s="1" t="s">
         <v>5</v>
       </c>
@@ -22900,7 +22857,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A177" s="1" t="s">
         <v>5</v>
       </c>
@@ -22920,7 +22877,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A178" s="1" t="s">
         <v>5</v>
       </c>
@@ -22940,7 +22897,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A179" s="1" t="s">
         <v>5</v>
       </c>

--- a/calculadora_final_srt.xlsx
+++ b/calculadora_final_srt.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alfredo\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://superintendenciart-my.sharepoint.com/personal/aalvarez_srt_gov_ar/Documents/Escritorio/AUDITOR/LABORAL/columnacalc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9CC0FF6-E062-4524-AD5D-D3BD93431275}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{B9CC0FF6-E062-4524-AD5D-D3BD93431275}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{12E12341-B9AE-42BC-AF5D-B0133DAAB9FB}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="-90" windowWidth="20660" windowHeight="10260" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="-90" windowWidth="20660" windowHeight="10260" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cervical" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5206" uniqueCount="581">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5206" uniqueCount="583">
   <si>
     <t>Sector</t>
   </si>
@@ -1770,6 +1770,12 @@
   </si>
   <si>
     <t xml:space="preserve">Fractura del extremo distal de la falange distal </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Luxación pura vertebral con espondilolistesis residual &lt; 50% (única o múltiple)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Luxación pura vertebral con espondilolistesis residual ≥ 50 % (única o múltiple)</t>
   </si>
 </sst>
 </file>
@@ -3506,7 +3512,7 @@
         <v>572</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>573</v>
+        <v>581</v>
       </c>
       <c r="G12" s="7">
         <v>15</v>
@@ -3529,7 +3535,7 @@
         <v>572</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="G13" s="7">
         <v>20</v>

--- a/calculadora_final_srt.xlsx
+++ b/calculadora_final_srt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://superintendenciart-my.sharepoint.com/personal/aalvarez_srt_gov_ar/Documents/Escritorio/AUDITOR/LABORAL/columnacalc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{B9CC0FF6-E062-4524-AD5D-D3BD93431275}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{12E12341-B9AE-42BC-AF5D-B0133DAAB9FB}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{B9CC0FF6-E062-4524-AD5D-D3BD93431275}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E95DBC7C-50BB-4A91-862A-EEFADD2C375D}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="-90" windowWidth="20660" windowHeight="10260" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="-90" windowWidth="20660" windowHeight="10260" firstSheet="6" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cervical" sheetId="1" r:id="rId1"/>
@@ -21,13 +21,14 @@
     <sheet name="Miembro Superior Izquierdo" sheetId="7" r:id="rId6"/>
     <sheet name="Miembro Inferior Derecho" sheetId="8" r:id="rId7"/>
     <sheet name="Miembro Inferior Izquierdo" sheetId="9" r:id="rId8"/>
+    <sheet name="Psiquiatría" sheetId="10" r:id="rId9"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5206" uniqueCount="583">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5231" uniqueCount="598">
   <si>
     <t>Sector</t>
   </si>
@@ -1776,13 +1777,58 @@
   </si>
   <si>
     <t xml:space="preserve"> Luxación pura vertebral con espondilolistesis residual ≥ 50 % (única o múltiple)</t>
+  </si>
+  <si>
+    <t>Descripción</t>
+  </si>
+  <si>
+    <t>Incapacidad (%)</t>
+  </si>
+  <si>
+    <t>Psiquiatría</t>
+  </si>
+  <si>
+    <t>Reacciones y Trastornos por Estrés</t>
+  </si>
+  <si>
+    <t>Grado I</t>
+  </si>
+  <si>
+    <t>Sin síntomas o síntomas aislados que no requieren tratamiento.</t>
+  </si>
+  <si>
+    <t>Grado II</t>
+  </si>
+  <si>
+    <t>Manifestaciones leves que no interfieren con la vida social o laboral.</t>
+  </si>
+  <si>
+    <t>Grado III</t>
+  </si>
+  <si>
+    <t>Requiere tratamiento. Interferencia moderada en la vida laboral.</t>
+  </si>
+  <si>
+    <t>Trastornos Depresivos</t>
+  </si>
+  <si>
+    <t>Episodio Leve</t>
+  </si>
+  <si>
+    <t>Ánimo depresivo, pérdida de interés, fatiga.</t>
+  </si>
+  <si>
+    <t>Episodio Moderado</t>
+  </si>
+  <si>
+    <t>Gran dificultad para continuar con actividades sociales/laborales.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1797,6 +1843,19 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -1858,7 +1917,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1868,6 +1927,12 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -22926,4 +22991,116 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76B2CD7F-D933-4AC7-8B55-4A08B0971BCD}">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultColWidth="22.40625" defaultRowHeight="86.35" customHeight="1" x14ac:dyDescent="0.75"/>
+  <sheetData>
+    <row r="1" spans="1:5" ht="86.35" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A1" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>556</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>583</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="86.35" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A2" s="10" t="s">
+        <v>585</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>586</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>587</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>588</v>
+      </c>
+      <c r="E2" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="86.35" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A3" s="10" t="s">
+        <v>585</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>586</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>589</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>590</v>
+      </c>
+      <c r="E3" s="10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="86.35" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A4" s="10" t="s">
+        <v>585</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>586</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>591</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>592</v>
+      </c>
+      <c r="E4" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="86.35" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A5" s="10" t="s">
+        <v>585</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>593</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>594</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>595</v>
+      </c>
+      <c r="E5" s="10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="86.35" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A6" s="10" t="s">
+        <v>585</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>593</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>596</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>597</v>
+      </c>
+      <c r="E6" s="10">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/calculadora_final_srt.xlsx
+++ b/calculadora_final_srt.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://superintendenciart-my.sharepoint.com/personal/aalvarez_srt_gov_ar/Documents/Escritorio/AUDITOR/LABORAL/columnacalc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{B9CC0FF6-E062-4524-AD5D-D3BD93431275}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E95DBC7C-50BB-4A91-862A-EEFADD2C375D}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{B9CC0FF6-E062-4524-AD5D-D3BD93431275}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ADF8FE58-2F4F-45E9-A91F-B2FBEC55F0CE}"/>
   <bookViews>
     <workbookView xWindow="-90" yWindow="-90" windowWidth="20660" windowHeight="10260" firstSheet="6" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5231" uniqueCount="598">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5228" uniqueCount="597">
   <si>
     <t>Sector</t>
   </si>
@@ -1782,53 +1782,50 @@
     <t>Descripción</t>
   </si>
   <si>
-    <t>Incapacidad (%)</t>
-  </si>
-  <si>
-    <t>Psiquiatría</t>
-  </si>
-  <si>
-    <t>Reacciones y Trastornos por Estrés</t>
-  </si>
-  <si>
     <t>Grado I</t>
   </si>
   <si>
-    <t>Sin síntomas o síntomas aislados que no requieren tratamiento.</t>
-  </si>
-  <si>
     <t>Grado II</t>
   </si>
   <si>
-    <t>Manifestaciones leves que no interfieren con la vida social o laboral.</t>
-  </si>
-  <si>
     <t>Grado III</t>
   </si>
   <si>
     <t>Requiere tratamiento. Interferencia moderada en la vida laboral.</t>
   </si>
   <si>
-    <t>Trastornos Depresivos</t>
-  </si>
-  <si>
-    <t>Episodio Leve</t>
-  </si>
-  <si>
     <t>Ánimo depresivo, pérdida de interés, fatiga.</t>
   </si>
   <si>
-    <t>Episodio Moderado</t>
-  </si>
-  <si>
     <t>Gran dificultad para continuar con actividades sociales/laborales.</t>
+  </si>
+  <si>
+    <t>Incapacidad</t>
+  </si>
+  <si>
+    <t>Desarrollo Vivencial Anormal (D.V.A.)</t>
+  </si>
+  <si>
+    <t>Grado I-II</t>
+  </si>
+  <si>
+    <t>Grado II-III</t>
+  </si>
+  <si>
+    <t>Grado III-IV</t>
+  </si>
+  <si>
+    <t>Grado IV</t>
+  </si>
+  <si>
+    <t>Grado IV con síntomas psicóticos</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1854,6 +1851,19 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -1917,7 +1927,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1932,6 +1942,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1948,6 +1964,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -22995,109 +23015,130 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76B2CD7F-D933-4AC7-8B55-4A08B0971BCD}">
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="22.40625" defaultRowHeight="86.35" customHeight="1" x14ac:dyDescent="0.75"/>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultColWidth="22.40625" defaultRowHeight="86.4" customHeight="1" x14ac:dyDescent="0.75"/>
   <sheetData>
-    <row r="1" spans="1:5" ht="86.35" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="9" t="s">
+    <row r="1" spans="1:5" ht="86.4" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
-        <v>556</v>
-      </c>
-      <c r="D1" s="9" t="s">
+      <c r="B1" s="11" t="s">
         <v>583</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="C1" s="11" t="s">
+        <v>590</v>
+      </c>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+    </row>
+    <row r="2" spans="1:5" ht="86.4" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A2" s="12" t="s">
+        <v>591</v>
+      </c>
+      <c r="B2" s="12" t="s">
         <v>584</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" ht="86.35" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A2" s="10" t="s">
+      <c r="C2" s="12">
+        <v>5</v>
+      </c>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+    </row>
+    <row r="3" spans="1:5" ht="86.4" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A3" s="12" t="s">
+        <v>591</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>592</v>
+      </c>
+      <c r="C3" s="12">
+        <v>10</v>
+      </c>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+    </row>
+    <row r="4" spans="1:5" ht="86.4" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A4" s="12" t="s">
+        <v>591</v>
+      </c>
+      <c r="B4" s="12" t="s">
         <v>585</v>
       </c>
-      <c r="B2" s="10" t="s">
-        <v>586</v>
-      </c>
-      <c r="C2" s="10" t="s">
+      <c r="C4" s="12">
+        <v>15</v>
+      </c>
+      <c r="D4" s="10" t="s">
         <v>587</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>588</v>
-      </c>
-      <c r="E2" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="86.35" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A3" s="10" t="s">
-        <v>585</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>586</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>589</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>590</v>
-      </c>
-      <c r="E3" s="10">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="86.35" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A4" s="10" t="s">
-        <v>585</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>586</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>591</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>592</v>
       </c>
       <c r="E4" s="10">
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="86.35" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A5" s="10" t="s">
-        <v>585</v>
-      </c>
-      <c r="B5" s="10" t="s">
+    <row r="5" spans="1:5" ht="86.4" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A5" s="12" t="s">
+        <v>591</v>
+      </c>
+      <c r="B5" s="12" t="s">
         <v>593</v>
       </c>
-      <c r="C5" s="10" t="s">
-        <v>594</v>
+      <c r="C5" s="12">
+        <v>20</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>595</v>
+        <v>588</v>
       </c>
       <c r="E5" s="10">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="86.35" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A6" s="10" t="s">
-        <v>585</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>593</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>596</v>
+    <row r="6" spans="1:5" ht="86.4" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A6" s="12" t="s">
+        <v>591</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>586</v>
+      </c>
+      <c r="C6" s="12">
+        <v>25</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>597</v>
+        <v>589</v>
       </c>
       <c r="E6" s="10">
         <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="86.4" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A7" s="12" t="s">
+        <v>591</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>594</v>
+      </c>
+      <c r="C7" s="12">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="86.4" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A8" s="12" t="s">
+        <v>591</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>595</v>
+      </c>
+      <c r="C8" s="12">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="86.4" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A9" s="12" t="s">
+        <v>591</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>596</v>
+      </c>
+      <c r="C9" s="12">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
